--- a/exports/Sildenafil_OTC_Switch_Forecast.xlsx
+++ b/exports/Sildenafil_OTC_Switch_Forecast.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="291">
   <si>
     <t>Sildenafil Rx-to-OTC Switch - Forecast Modell</t>
   </si>
@@ -75,7 +75,7 @@
     <t>Therapiequote aktuell</t>
   </si>
   <si>
-    <t>Nur 1/3 werden behandelt</t>
+    <t>Nur 30% werden behandelt (May et al. 2007)</t>
   </si>
   <si>
     <t>Therapieluecke</t>
@@ -183,7 +183,7 @@
     <t>Online-Wachstum p.a. (Pp.)</t>
   </si>
   <si>
-    <t>CAGR OTC Online: 12.6%</t>
+    <t>ABDA ZDF 2024: ~+1.5-2 Pp./Jahr</t>
   </si>
   <si>
     <t>Apothekenmarge (stationaer)</t>
@@ -219,28 +219,7 @@
     <t>Marke ist 1.8x teurer als Generika OTC</t>
   </si>
   <si>
-    <t>6. TELEMEDIZIN-DISRUPTION</t>
-  </si>
-  <si>
-    <t>Telemed. Umsatz/Mon. (EUR)</t>
-  </si>
-  <si>
-    <t>Zava, GoSpring, TeleClinic etc.</t>
-  </si>
-  <si>
-    <t>Telemed. Umsatzrueckgang</t>
-  </si>
-  <si>
-    <t>OTC entfernt Rezeptpflicht als USP</t>
-  </si>
-  <si>
-    <t>Telemed. Retention</t>
-  </si>
-  <si>
-    <t>Verbleibend: Beratung, Diagnostik</t>
-  </si>
-  <si>
-    <t>7. SZENARIO-DEFINITIONEN</t>
+    <t>6. SZENARIO-DEFINITIONEN</t>
   </si>
   <si>
     <t>Parameter</t>
@@ -297,7 +276,7 @@
     <t>Therapiequote</t>
   </si>
   <si>
-    <t>Nur 33% erhalten Behandlung</t>
+    <t>Nur 30% erhalten Behandlung (May et al. 2007)</t>
   </si>
   <si>
     <t>Primaere Barriere</t>
@@ -407,33 +386,6 @@
     <t>USD 260 Mio. (CAGR 7.2%)</t>
   </si>
   <si>
-    <t>Telemedizin ED-Plattformen</t>
-  </si>
-  <si>
-    <t>Zava (Hims)</t>
-  </si>
-  <si>
-    <t>2M Patienten (2018), ED-Konsult. EUR 29</t>
-  </si>
-  <si>
-    <t>GoSpring</t>
-  </si>
-  <si>
-    <t>11.456 ED-Pat. (Mai-Nov 2019), 80% Sildenafil</t>
-  </si>
-  <si>
-    <t>TeleClinic</t>
-  </si>
-  <si>
-    <t>Video-Konsultation + Rx</t>
-  </si>
-  <si>
-    <t>Disruption durch OTC</t>
-  </si>
-  <si>
-    <t>Kerngeschaeft (Rx) entfaellt</t>
-  </si>
-  <si>
     <t>BfArM SVA-Entscheidungen</t>
   </si>
   <si>
@@ -664,7 +616,7 @@
     <t>Nature / Braun et al.</t>
   </si>
   <si>
-    <t>33% (2/3 unbehandelt)</t>
+    <t>30% (May et al. 2007; Arnold 2023)</t>
   </si>
   <si>
     <t>Viatris DE / Handelsblatt</t>
@@ -805,7 +757,7 @@
     <t>Online-Anteil</t>
   </si>
   <si>
-    <t>40% (steigend)</t>
+    <t>45% (steigend)</t>
   </si>
   <si>
     <t>Anonymitaet = Kernvorteil bei ED/Stigma</t>
@@ -814,21 +766,12 @@
     <t>Markenanteil</t>
   </si>
   <si>
-    <t>45% (sinkend)</t>
+    <t>25% (sinkend)</t>
   </si>
   <si>
     <t>Viagra-Brand stark, aber Generikadruck</t>
   </si>
   <si>
-    <t>Telemed. Verlust</t>
-  </si>
-  <si>
-    <t>60%</t>
-  </si>
-  <si>
-    <t>Rx-Pflicht = Kern-USP der Plattformen</t>
-  </si>
-  <si>
     <t>Marketing</t>
   </si>
   <si>
@@ -886,19 +829,10 @@
     <t>ED-Stigma treibt anonyme Kanaele</t>
   </si>
   <si>
-    <t>Telemed.-Disruption</t>
-  </si>
-  <si>
-    <t>Exp. Decay + Pivot-Retention (15%)</t>
-  </si>
-  <si>
-    <t>Zava/GoSpring verlieren Rx-Geschaeft</t>
-  </si>
-  <si>
     <t>Markenanteil-Erosion</t>
   </si>
   <si>
-    <t>Linear: -3Pp/Jahr, Floor 15%</t>
+    <t>Linear: -3Pp/Jahr, Floor 10%</t>
   </si>
   <si>
     <t>Generikadruck analog UK</t>
@@ -968,15 +902,6 @@
   </si>
   <si>
     <t>SEMPORA / IQVIA</t>
-  </si>
-  <si>
-    <t>Telemedizin-Umsatzdaten</t>
-  </si>
-  <si>
-    <t>Tatsaechliche ED-Umsaetze Zava/GoSpring DE</t>
-  </si>
-  <si>
-    <t>Firmenberichte (nicht-oeffentlich)</t>
   </si>
   <si>
     <t>BfArM Switch-Wahrscheinlichkeit</t>
@@ -1545,184 +1470,184 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="60"/>
                 <c:pt idx="0">
-                  <c:v>89066</c:v>
+                  <c:v>89067</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>139415</c:v>
+                  <c:v>139420</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>176821</c:v>
+                  <c:v>176829</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>231928</c:v>
+                  <c:v>231939</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>313561</c:v>
+                  <c:v>313578</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>414109</c:v>
+                  <c:v>414132</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>486946</c:v>
+                  <c:v>486972</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>556364</c:v>
+                  <c:v>556391</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>616990</c:v>
+                  <c:v>617016</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>700626</c:v>
+                  <c:v>700647</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>776030</c:v>
+                  <c:v>776043</c:v>
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>884315</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>848095</c:v>
+                  <c:v>848079</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1033452</c:v>
+                  <c:v>1033408</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1019570</c:v>
+                  <c:v>1019501</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1045460</c:v>
+                  <c:v>1045359</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1116533</c:v>
+                  <c:v>1116390</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1183463</c:v>
+                  <c:v>1183270</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1140655</c:v>
+                  <c:v>1140428</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1093877</c:v>
+                  <c:v>1093616</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1044323</c:v>
+                  <c:v>1044029</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>1046537</c:v>
+                  <c:v>1046195</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>1047539</c:v>
+                  <c:v>1047146</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>1101349</c:v>
+                  <c:v>1100880</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>993449</c:v>
+                  <c:v>992974</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>1153286</c:v>
+                  <c:v>1152667</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>1098239</c:v>
+                  <c:v>1097585</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>1096521</c:v>
+                  <c:v>1095800</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>1147941</c:v>
+                  <c:v>1147112</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>1199009</c:v>
+                  <c:v>1198062</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>1143496</c:v>
+                  <c:v>1142513</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>1088115</c:v>
+                  <c:v>1087102</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>1032896</c:v>
+                  <c:v>1031858</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>1030647</c:v>
+                  <c:v>1029532</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>1028364</c:v>
+                  <c:v>1027169</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>1078607</c:v>
+                  <c:v>1077263</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>971283</c:v>
+                  <c:v>969993</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>1125999</c:v>
+                  <c:v>1124399</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>1071194</c:v>
+                  <c:v>1069577</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>1068692</c:v>
+                  <c:v>1066979</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>1118131</c:v>
+                  <c:v>1116230</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>1167315</c:v>
+                  <c:v>1165214</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>1112823</c:v>
+                  <c:v>1110711</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>1058566</c:v>
+                  <c:v>1056450</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>1004545</c:v>
+                  <c:v>1002434</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>1002103</c:v>
+                  <c:v>999889</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>999652</c:v>
+                  <c:v>997334</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>1048285</c:v>
+                  <c:v>1045734</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>943758</c:v>
+                  <c:v>941360</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>1093935</c:v>
+                  <c:v>1091016</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>1040484</c:v>
+                  <c:v>1037587</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>1037867</c:v>
+                  <c:v>1034850</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>1085705</c:v>
+                  <c:v>1082411</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>1133282</c:v>
+                  <c:v>1129696</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>1080175</c:v>
+                  <c:v>1076623</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>1027316</c:v>
+                  <c:v>1023806</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>974703</c:v>
+                  <c:v>971249</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>972165</c:v>
+                  <c:v>968589</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>969620</c:v>
+                  <c:v>965919</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>1016633</c:v>
+                  <c:v>1012606</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1935,184 +1860,184 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="60"/>
                 <c:pt idx="0">
-                  <c:v>76666</c:v>
+                  <c:v>76667</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>120815</c:v>
+                  <c:v>120819</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>154264</c:v>
+                  <c:v>154271</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>203705</c:v>
+                  <c:v>203715</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>277260</c:v>
+                  <c:v>277275</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>368634</c:v>
+                  <c:v>368654</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>436389</c:v>
+                  <c:v>436413</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>501954</c:v>
+                  <c:v>501979</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>560394</c:v>
+                  <c:v>560418</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>640635</c:v>
+                  <c:v>640654</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>714349</c:v>
+                  <c:v>714361</c:v>
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>819493</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>791203</c:v>
+                  <c:v>791188</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>970595</c:v>
+                  <c:v>970553</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>963979</c:v>
+                  <c:v>963914</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>995085</c:v>
+                  <c:v>994988</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1069857</c:v>
+                  <c:v>1069719</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1141586</c:v>
+                  <c:v>1141401</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1107664</c:v>
+                  <c:v>1107443</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1069353</c:v>
+                  <c:v>1069098</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1027746</c:v>
+                  <c:v>1027457</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>1036819</c:v>
+                  <c:v>1036480</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>1044758</c:v>
+                  <c:v>1044367</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>1105776</c:v>
+                  <c:v>1105305</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>1004117</c:v>
+                  <c:v>1003636</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>1173468</c:v>
+                  <c:v>1172839</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>1124934</c:v>
+                  <c:v>1124264</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>1130687</c:v>
+                  <c:v>1129944</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>1191628</c:v>
+                  <c:v>1190767</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>1252965</c:v>
+                  <c:v>1251975</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>1202946</c:v>
+                  <c:v>1201912</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>1152343</c:v>
+                  <c:v>1151270</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>1101181</c:v>
+                  <c:v>1100075</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>1106135</c:v>
+                  <c:v>1104939</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>1111069</c:v>
+                  <c:v>1109778</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>1173150</c:v>
+                  <c:v>1171688</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>1063489</c:v>
+                  <c:v>1062077</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>1241144</c:v>
+                  <c:v>1239380</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>1188639</c:v>
+                  <c:v>1186845</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>1193803</c:v>
+                  <c:v>1191889</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>1257394</c:v>
+                  <c:v>1255257</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>1321498</c:v>
+                  <c:v>1319119</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>1268250</c:v>
+                  <c:v>1265843</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>1214501</c:v>
+                  <c:v>1212073</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>1160249</c:v>
+                  <c:v>1157811</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>1165191</c:v>
+                  <c:v>1162618</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>1170140</c:v>
+                  <c:v>1167428</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>1235304</c:v>
+                  <c:v>1232298</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>1119596</c:v>
+                  <c:v>1116751</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>1306471</c:v>
+                  <c:v>1302985</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>1250986</c:v>
+                  <c:v>1247503</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>1256230</c:v>
+                  <c:v>1252579</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>1322973</c:v>
+                  <c:v>1318959</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>1390241</c:v>
+                  <c:v>1385843</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>1334017</c:v>
+                  <c:v>1329629</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>1277283</c:v>
+                  <c:v>1272920</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>1220039</c:v>
+                  <c:v>1215715</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>1225071</c:v>
+                  <c:v>1220564</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>1230111</c:v>
+                  <c:v>1225416</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>1298466</c:v>
+                  <c:v>1293323</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2419,184 +2344,184 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="60"/>
                 <c:pt idx="0">
-                  <c:v>867839</c:v>
+                  <c:v>776210</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>867679</c:v>
+                  <c:v>900221</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>867519</c:v>
+                  <c:v>852659</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>867360</c:v>
+                  <c:v>848340</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>867200</c:v>
+                  <c:v>886583</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>867042</c:v>
+                  <c:v>924778</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>866883</c:v>
+                  <c:v>879209</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>866725</c:v>
+                  <c:v>834246</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>866567</c:v>
+                  <c:v>789826</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>866410</c:v>
+                  <c:v>787336</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>866253</c:v>
+                  <c:v>785044</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>866097</c:v>
+                  <c:v>824142</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>865940</c:v>
+                  <c:v>739889</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>865784</c:v>
+                  <c:v>861231</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>865629</c:v>
+                  <c:v>818490</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>865474</c:v>
+                  <c:v>816899</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>865319</c:v>
+                  <c:v>856206</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>865165</c:v>
+                  <c:v>895496</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>865010</c:v>
+                  <c:v>853490</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>864857</c:v>
+                  <c:v>811707</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>864703</c:v>
+                  <c:v>770124</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>864550</c:v>
+                  <c:v>769206</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>864398</c:v>
+                  <c:v>768362</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>864245</c:v>
+                  <c:v>807984</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>864093</c:v>
+                  <c:v>726509</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>863942</c:v>
+                  <c:v>846866</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>863790</c:v>
+                  <c:v>805902</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>863640</c:v>
+                  <c:v>805316</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>863489</c:v>
+                  <c:v>845016</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>863339</c:v>
+                  <c:v>884708</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>863189</c:v>
+                  <c:v>844015</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>863039</c:v>
+                  <c:v>803403</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>862890</c:v>
+                  <c:v>762866</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>862741</c:v>
+                  <c:v>762528</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>862593</c:v>
+                  <c:v>762217</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>862445</c:v>
+                  <c:v>802032</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>862297</c:v>
+                  <c:v>721579</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>862150</c:v>
+                  <c:v>841575</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>862002</c:v>
+                  <c:v>801265</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>861856</c:v>
+                  <c:v>801049</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>861709</c:v>
+                  <c:v>840893</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>861563</c:v>
+                  <c:v>880734</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>861417</c:v>
+                  <c:v>840524</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>861272</c:v>
+                  <c:v>800344</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>861127</c:v>
+                  <c:v>760192</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>860982</c:v>
+                  <c:v>760067</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>860838</c:v>
+                  <c:v>759953</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>860694</c:v>
+                  <c:v>799839</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>860550</c:v>
+                  <c:v>719763</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>860406</c:v>
+                  <c:v>839625</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>860263</c:v>
+                  <c:v>799557</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>860121</c:v>
+                  <c:v>799477</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>859978</c:v>
+                  <c:v>839374</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>859836</c:v>
+                  <c:v>879270</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>859694</c:v>
+                  <c:v>839238</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>859553</c:v>
+                  <c:v>799217</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>859412</c:v>
+                  <c:v>759207</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>859271</c:v>
+                  <c:v>759161</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>859131</c:v>
+                  <c:v>759119</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>858990</c:v>
+                  <c:v>799031</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2814,184 +2739,184 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="60"/>
                 <c:pt idx="0">
-                  <c:v>165731</c:v>
+                  <c:v>165734</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>260230</c:v>
+                  <c:v>260238</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>331086</c:v>
+                  <c:v>331100</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>435633</c:v>
+                  <c:v>435655</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>590821</c:v>
+                  <c:v>590853</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>782743</c:v>
+                  <c:v>782786</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>923335</c:v>
+                  <c:v>923385</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1058318</c:v>
+                  <c:v>1058370</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1177385</c:v>
+                  <c:v>1177434</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1341260</c:v>
+                  <c:v>1341301</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1490378</c:v>
+                  <c:v>1490403</c:v>
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>1703807</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1639299</c:v>
+                  <c:v>1639267</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2004047</c:v>
+                  <c:v>2003961</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1983550</c:v>
+                  <c:v>1983414</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2040544</c:v>
+                  <c:v>2040347</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2186390</c:v>
+                  <c:v>2186110</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2325049</c:v>
+                  <c:v>2324671</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2248320</c:v>
+                  <c:v>2247871</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2163231</c:v>
+                  <c:v>2162714</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2072069</c:v>
+                  <c:v>2071486</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>2083356</c:v>
+                  <c:v>2082675</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>2092297</c:v>
+                  <c:v>2091513</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>2207125</c:v>
+                  <c:v>2206185</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>1997566</c:v>
+                  <c:v>1996611</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>2326754</c:v>
+                  <c:v>2325506</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>2223172</c:v>
+                  <c:v>2221849</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>2227208</c:v>
+                  <c:v>2225745</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>2339569</c:v>
+                  <c:v>2337879</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>2451974</c:v>
+                  <c:v>2450036</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>2346442</c:v>
+                  <c:v>2344425</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>2240457</c:v>
+                  <c:v>2238372</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>2134077</c:v>
+                  <c:v>2131934</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>2136783</c:v>
+                  <c:v>2134471</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>2139433</c:v>
+                  <c:v>2136947</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>2251757</c:v>
+                  <c:v>2248951</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>2034772</c:v>
+                  <c:v>2032070</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>2367143</c:v>
+                  <c:v>2363778</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>2259834</c:v>
+                  <c:v>2256422</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>2262494</c:v>
+                  <c:v>2258868</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>2375525</c:v>
+                  <c:v>2371487</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>2488813</c:v>
+                  <c:v>2484333</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>2381073</c:v>
+                  <c:v>2376553</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>2273067</c:v>
+                  <c:v>2268523</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>2164794</c:v>
+                  <c:v>2160246</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>2167294</c:v>
+                  <c:v>2162507</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>2169792</c:v>
+                  <c:v>2164762</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>2283589</c:v>
+                  <c:v>2278032</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>2063355</c:v>
+                  <c:v>2058111</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>2400406</c:v>
+                  <c:v>2394001</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>2291470</c:v>
+                  <c:v>2285089</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>2294096</c:v>
+                  <c:v>2287429</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>2408678</c:v>
+                  <c:v>2401371</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>2523523</c:v>
+                  <c:v>2515539</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>2414192</c:v>
+                  <c:v>2406252</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>2304599</c:v>
+                  <c:v>2296727</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>2194743</c:v>
+                  <c:v>2186964</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>2197237</c:v>
+                  <c:v>2189153</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>2199731</c:v>
+                  <c:v>2191335</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>2315100</c:v>
+                  <c:v>2305929</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3294,184 +3219,184 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="60"/>
                 <c:pt idx="0">
-                  <c:v>40880</c:v>
+                  <c:v>41019</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>63323</c:v>
+                  <c:v>63758</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>79461</c:v>
+                  <c:v>80292</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>103100</c:v>
+                  <c:v>104557</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>137858</c:v>
+                  <c:v>140328</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>180031</c:v>
+                  <c:v>183955</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>209289</c:v>
+                  <c:v>214687</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>236358</c:v>
+                  <c:v>243425</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>259025</c:v>
+                  <c:v>267866</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>290606</c:v>
+                  <c:v>301793</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>317947</c:v>
+                  <c:v>331615</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>357799</c:v>
+                  <c:v>374838</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>338788</c:v>
+                  <c:v>356541</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>407490</c:v>
+                  <c:v>430852</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>396710</c:v>
+                  <c:v>421475</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>401307</c:v>
+                  <c:v>428473</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>422702</c:v>
+                  <c:v>453618</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>441759</c:v>
+                  <c:v>476558</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>419686</c:v>
+                  <c:v>455194</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>396592</c:v>
+                  <c:v>432543</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>372972</c:v>
+                  <c:v>409118</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>368060</c:v>
+                  <c:v>406122</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>362665</c:v>
+                  <c:v>402616</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>375211</c:v>
+                  <c:v>419175</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>332928</c:v>
+                  <c:v>374365</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>380036</c:v>
+                  <c:v>430219</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>355708</c:v>
+                  <c:v>405487</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>348929</c:v>
+                  <c:v>400634</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>358734</c:v>
+                  <c:v>414974</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>367796</c:v>
+                  <c:v>428756</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>344145</c:v>
+                  <c:v>404413</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>321132</c:v>
+                  <c:v>380523</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>298771</c:v>
+                  <c:v>357099</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>292027</c:v>
+                  <c:v>352188</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>285258</c:v>
+                  <c:v>347254</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>292728</c:v>
+                  <c:v>359832</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>257738</c:v>
+                  <c:v>320051</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>291948</c:v>
+                  <c:v>366386</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>271180</c:v>
+                  <c:v>344104</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>263958</c:v>
+                  <c:v>338830</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>269226</c:v>
+                  <c:v>349794</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>273769</c:v>
+                  <c:v>360228</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>253981</c:v>
+                  <c:v>338659</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>234884</c:v>
+                  <c:v>317593</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>216479</c:v>
+                  <c:v>297034</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>216729</c:v>
+                  <c:v>291938</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>216979</c:v>
+                  <c:v>286831</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>228359</c:v>
+                  <c:v>296144</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>206336</c:v>
+                  <c:v>262409</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>240041</c:v>
+                  <c:v>299250</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>229147</c:v>
+                  <c:v>279923</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>229410</c:v>
+                  <c:v>274491</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>240868</c:v>
+                  <c:v>282161</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>252352</c:v>
+                  <c:v>289287</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>241419</c:v>
+                  <c:v>270703</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>230460</c:v>
+                  <c:v>252640</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>219474</c:v>
+                  <c:v>235099</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>219724</c:v>
+                  <c:v>229861</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>219973</c:v>
+                  <c:v>224612</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>231510</c:v>
+                  <c:v>230593</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3684,184 +3609,184 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="60"/>
                 <c:pt idx="0">
-                  <c:v>124851</c:v>
+                  <c:v>124715</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>196907</c:v>
+                  <c:v>196480</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>251625</c:v>
+                  <c:v>250808</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>332533</c:v>
+                  <c:v>331098</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>452963</c:v>
+                  <c:v>450525</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>602712</c:v>
+                  <c:v>598831</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>714046</c:v>
+                  <c:v>708698</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>821960</c:v>
+                  <c:v>814945</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>918360</c:v>
+                  <c:v>909568</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1050654</c:v>
+                  <c:v>1039508</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1172431</c:v>
+                  <c:v>1158788</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1346008</c:v>
+                  <c:v>1328969</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1300511</c:v>
+                  <c:v>1282726</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1596557</c:v>
+                  <c:v>1573109</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1586840</c:v>
+                  <c:v>1561939</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1639237</c:v>
+                  <c:v>1611874</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1763688</c:v>
+                  <c:v>1732492</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1883290</c:v>
+                  <c:v>1848113</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1828634</c:v>
+                  <c:v>1792677</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1766639</c:v>
+                  <c:v>1730171</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1699097</c:v>
+                  <c:v>1662368</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>1715296</c:v>
+                  <c:v>1676553</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>1729632</c:v>
+                  <c:v>1688897</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>1831914</c:v>
+                  <c:v>1787010</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>1664638</c:v>
+                  <c:v>1622246</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>1946718</c:v>
+                  <c:v>1895287</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>1867464</c:v>
+                  <c:v>1816362</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>1878279</c:v>
+                  <c:v>1825111</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>1980835</c:v>
+                  <c:v>1922905</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>2084178</c:v>
+                  <c:v>2021280</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>2002297</c:v>
+                  <c:v>1940012</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>1919325</c:v>
+                  <c:v>1857849</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>1835306</c:v>
+                  <c:v>1774835</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>1844756</c:v>
+                  <c:v>1782283</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>1854175</c:v>
+                  <c:v>1789693</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>1959029</c:v>
+                  <c:v>1889119</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>1777034</c:v>
+                  <c:v>1712019</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>2075195</c:v>
+                  <c:v>1997392</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>1988654</c:v>
+                  <c:v>1912318</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>1998536</c:v>
+                  <c:v>1920038</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>2106299</c:v>
+                  <c:v>2021693</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>2215044</c:v>
+                  <c:v>2124105</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>2127092</c:v>
+                  <c:v>2037894</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>2038183</c:v>
+                  <c:v>1950930</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>1948315</c:v>
+                  <c:v>1863212</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>1950565</c:v>
+                  <c:v>1870569</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>1952813</c:v>
+                  <c:v>1877931</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>2055230</c:v>
+                  <c:v>1981888</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>1857020</c:v>
+                  <c:v>1795702</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>2160365</c:v>
+                  <c:v>2094751</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>2062323</c:v>
+                  <c:v>2005166</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>2064686</c:v>
+                  <c:v>2012938</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>2167810</c:v>
+                  <c:v>2119210</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>2271171</c:v>
+                  <c:v>2226252</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>2172773</c:v>
+                  <c:v>2135549</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>2074139</c:v>
+                  <c:v>2044087</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>1975269</c:v>
+                  <c:v>1951865</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>1977513</c:v>
+                  <c:v>1959292</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>1979758</c:v>
+                  <c:v>1966723</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>2083590</c:v>
+                  <c:v>2075336</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4318,7 +4243,7 @@
   <sheetPr>
     <tabColor rgb="FFE0B800"/>
   </sheetPr>
-  <dimension ref="B2:E55"/>
+  <dimension ref="B2:E49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="3.7109375" customWidth="1"/>
@@ -4408,7 +4333,7 @@
         <v>17</v>
       </c>
       <c r="C11" s="8">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>18</v>
@@ -4419,7 +4344,7 @@
         <v>19</v>
       </c>
       <c r="C12" s="7">
-        <v>3350000</v>
+        <v>3500000</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>20</v>
@@ -4605,7 +4530,7 @@
         <v>53</v>
       </c>
       <c r="C33" s="8">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="D33" s="6" t="s">
         <v>54</v>
@@ -4645,7 +4570,7 @@
         <v>60</v>
       </c>
       <c r="C38" s="8">
-        <v>0.45</v>
+        <v>0.25</v>
       </c>
       <c r="D38" s="6" t="s">
         <v>61</v>
@@ -4681,159 +4606,105 @@
       <c r="D42" s="3"/>
     </row>
     <row r="43" spans="2:5">
-      <c r="B43" s="4" t="s">
+      <c r="B43" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="C43" s="7">
-        <v>4500000</v>
-      </c>
-      <c r="D43" s="6" t="s">
+      <c r="C43" s="10" t="s">
         <v>68</v>
+      </c>
+      <c r="D43" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="E43" s="10" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="44" spans="2:5">
       <c r="B44" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="C44" s="8">
-        <v>0.6</v>
-      </c>
-      <c r="D44" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="C44" s="7">
+        <v>1200000</v>
+      </c>
+      <c r="D44" s="7">
+        <v>2100000</v>
+      </c>
+      <c r="E44" s="7">
+        <v>2700000</v>
       </c>
     </row>
     <row r="45" spans="2:5">
       <c r="B45" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="C45" s="8">
-        <v>0.15</v>
-      </c>
-      <c r="D45" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C45" s="7">
+        <v>24</v>
+      </c>
+      <c r="D45" s="7">
+        <v>18</v>
+      </c>
+      <c r="E45" s="7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="46" spans="2:5">
+      <c r="B46" s="4" t="s">
         <v>72</v>
       </c>
+      <c r="C46" s="7">
+        <v>300000</v>
+      </c>
+      <c r="D46" s="7">
+        <v>500000</v>
+      </c>
+      <c r="E46" s="7">
+        <v>750000</v>
+      </c>
     </row>
     <row r="47" spans="2:5">
-      <c r="B47" s="3" t="s">
+      <c r="B47" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="C47" s="3"/>
-      <c r="D47" s="3"/>
+      <c r="C47" s="8">
+        <v>0.55</v>
+      </c>
+      <c r="D47" s="8">
+        <v>0.63</v>
+      </c>
+      <c r="E47" s="8">
+        <v>0.7</v>
+      </c>
     </row>
     <row r="48" spans="2:5">
-      <c r="B48" s="10" t="s">
+      <c r="B48" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="C48" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="D48" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="E48" s="10" t="s">
-        <v>77</v>
+      <c r="C48" s="8">
+        <v>0.12</v>
+      </c>
+      <c r="D48" s="8">
+        <v>0.08</v>
+      </c>
+      <c r="E48" s="8">
+        <v>0.05</v>
       </c>
     </row>
     <row r="49" spans="2:5">
       <c r="B49" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="C49" s="7">
-        <v>1200000</v>
-      </c>
-      <c r="D49" s="7">
-        <v>2100000</v>
-      </c>
-      <c r="E49" s="7">
-        <v>2700000</v>
-      </c>
-    </row>
-    <row r="50" spans="2:5">
-      <c r="B50" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="C50" s="7">
-        <v>4.99</v>
-      </c>
-      <c r="D50" s="7">
-        <v>5.99</v>
-      </c>
-      <c r="E50" s="7">
-        <v>6.99</v>
-      </c>
-    </row>
-    <row r="51" spans="2:5">
-      <c r="B51" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C51" s="7">
-        <v>24</v>
-      </c>
-      <c r="D51" s="7">
-        <v>18</v>
-      </c>
-      <c r="E51" s="7">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="52" spans="2:5">
-      <c r="B52" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="C52" s="7">
-        <v>300000</v>
-      </c>
-      <c r="D52" s="7">
-        <v>500000</v>
-      </c>
-      <c r="E52" s="7">
-        <v>750000</v>
-      </c>
-    </row>
-    <row r="53" spans="2:5">
-      <c r="B53" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="C53" s="8">
-        <v>0.55</v>
-      </c>
-      <c r="D53" s="8">
-        <v>0.63</v>
-      </c>
-      <c r="E53" s="8">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="54" spans="2:5">
-      <c r="B54" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="C54" s="8">
-        <v>0.12</v>
-      </c>
-      <c r="D54" s="8">
-        <v>0.08</v>
-      </c>
-      <c r="E54" s="8">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="55" spans="2:5">
-      <c r="B55" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C55" s="8">
+        <v>75</v>
+      </c>
+      <c r="C49" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="D49" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="E49" s="8">
         <v>0.35</v>
       </c>
-      <c r="D55" s="8">
-        <v>0.45</v>
-      </c>
-      <c r="E55" s="8">
-        <v>0.5</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="8">
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="B5:D5"/>
@@ -4842,7 +4713,6 @@
     <mergeCell ref="B30:D30"/>
     <mergeCell ref="B37:D37"/>
     <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B47:D47"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4853,7 +4723,7 @@
   <sheetPr>
     <tabColor rgb="FF1E3A5F"/>
   </sheetPr>
-  <dimension ref="B2:F40"/>
+  <dimension ref="B2:F34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="3.7109375" customWidth="1"/>
@@ -4863,7 +4733,7 @@
   <sheetData>
     <row r="2" spans="2:6">
       <c r="B2" s="1" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -4872,7 +4742,7 @@
     </row>
     <row r="4" spans="2:6">
       <c r="B4" s="3" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
@@ -4881,10 +4751,10 @@
     </row>
     <row r="5" spans="2:6">
       <c r="B5" s="4" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="D5" s="11"/>
       <c r="E5" s="11"/>
@@ -4892,10 +4762,10 @@
     </row>
     <row r="6" spans="2:6">
       <c r="B6" s="4" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="D6" s="11"/>
       <c r="E6" s="11"/>
@@ -4903,10 +4773,10 @@
     </row>
     <row r="7" spans="2:6">
       <c r="B7" s="4" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="D7" s="11"/>
       <c r="E7" s="11"/>
@@ -4914,10 +4784,10 @@
     </row>
     <row r="8" spans="2:6">
       <c r="B8" s="4" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="D8" s="11"/>
       <c r="E8" s="11"/>
@@ -4925,10 +4795,10 @@
     </row>
     <row r="9" spans="2:6">
       <c r="B9" s="4" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="D9" s="11"/>
       <c r="E9" s="11"/>
@@ -4939,7 +4809,7 @@
         <v>32</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="D10" s="11"/>
       <c r="E10" s="11"/>
@@ -4947,7 +4817,7 @@
     </row>
     <row r="12" spans="2:6">
       <c r="B12" s="3" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="C12" s="3"/>
       <c r="D12" s="3"/>
@@ -4959,16 +4829,16 @@
         <v>6</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14" spans="2:6">
@@ -4979,69 +4849,69 @@
         <v>0.55</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="E14" s="13">
         <v>1.5</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
     </row>
     <row r="15" spans="2:6">
       <c r="B15" s="4" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="C15" s="12">
         <v>0.36</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="E15" s="13">
         <v>1.8</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
     </row>
     <row r="16" spans="2:6">
       <c r="B16" s="4" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="C16" s="12">
         <v>0.04</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="E16" s="13">
         <v>2.5</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
     </row>
     <row r="17" spans="2:6">
       <c r="B17" s="4" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="C17" s="12">
         <v>0.01</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="E17" s="13">
         <v>5</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
     </row>
     <row r="19" spans="2:6">
       <c r="B19" s="3" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
@@ -5050,10 +4920,10 @@
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="4" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="D20" s="11"/>
       <c r="E20" s="11"/>
@@ -5061,10 +4931,10 @@
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="4" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="D21" s="11"/>
       <c r="E21" s="11"/>
@@ -5072,10 +4942,10 @@
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="4" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="D22" s="11"/>
       <c r="E22" s="11"/>
@@ -5083,10 +4953,10 @@
     </row>
     <row r="23" spans="2:6">
       <c r="B23" s="4" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="D23" s="11"/>
       <c r="E23" s="11"/>
@@ -5094,10 +4964,10 @@
     </row>
     <row r="24" spans="2:6">
       <c r="B24" s="4" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="D24" s="11"/>
       <c r="E24" s="11"/>
@@ -5105,10 +4975,10 @@
     </row>
     <row r="25" spans="2:6">
       <c r="B25" s="4" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="D25" s="11"/>
       <c r="E25" s="11"/>
@@ -5116,10 +4986,10 @@
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="4" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="D26" s="11"/>
       <c r="E26" s="11"/>
@@ -5127,10 +4997,10 @@
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="4" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="D27" s="11"/>
       <c r="E27" s="11"/>
@@ -5138,7 +5008,7 @@
     </row>
     <row r="29" spans="2:6">
       <c r="B29" s="3" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
@@ -5147,10 +5017,10 @@
     </row>
     <row r="30" spans="2:6">
       <c r="B30" s="4" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="D30" s="11"/>
       <c r="E30" s="11"/>
@@ -5158,10 +5028,10 @@
     </row>
     <row r="31" spans="2:6">
       <c r="B31" s="4" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="D31" s="11"/>
       <c r="E31" s="11"/>
@@ -5169,10 +5039,10 @@
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="4" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="D32" s="11"/>
       <c r="E32" s="11"/>
@@ -5180,81 +5050,28 @@
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="4" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="D33" s="11"/>
       <c r="E33" s="11"/>
       <c r="F33" s="11"/>
     </row>
-    <row r="35" spans="2:6">
-      <c r="B35" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="C35" s="3"/>
-      <c r="D35" s="3"/>
-      <c r="E35" s="3"/>
-      <c r="F35" s="3"/>
-    </row>
-    <row r="36" spans="2:6">
-      <c r="B36" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="C36" s="11" t="s">
-        <v>139</v>
-      </c>
-      <c r="D36" s="11"/>
-      <c r="E36" s="11"/>
-      <c r="F36" s="11"/>
-    </row>
-    <row r="37" spans="2:6">
-      <c r="B37" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="C37" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="D37" s="11"/>
-      <c r="E37" s="11"/>
-      <c r="F37" s="11"/>
-    </row>
-    <row r="38" spans="2:6">
-      <c r="B38" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="C38" s="11" t="s">
-        <v>143</v>
-      </c>
-      <c r="D38" s="11"/>
-      <c r="E38" s="11"/>
-      <c r="F38" s="11"/>
-    </row>
-    <row r="39" spans="2:6">
-      <c r="B39" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="C39" s="11" t="s">
-        <v>145</v>
-      </c>
-      <c r="D39" s="11"/>
-      <c r="E39" s="11"/>
-      <c r="F39" s="11"/>
-    </row>
-    <row r="40" spans="2:6">
-      <c r="B40" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="C40" s="11" t="s">
-        <v>147</v>
-      </c>
-      <c r="D40" s="11"/>
-      <c r="E40" s="11"/>
-      <c r="F40" s="11"/>
+    <row r="34" spans="2:6">
+      <c r="B34" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="C34" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="D34" s="11"/>
+      <c r="E34" s="11"/>
+      <c r="F34" s="11"/>
     </row>
   </sheetData>
-  <mergeCells count="29">
+  <mergeCells count="24">
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="B4:F4"/>
     <mergeCell ref="C5:F5"/>
@@ -5278,12 +5095,7 @@
     <mergeCell ref="C31:F31"/>
     <mergeCell ref="C32:F32"/>
     <mergeCell ref="C33:F33"/>
-    <mergeCell ref="B35:F35"/>
-    <mergeCell ref="C36:F36"/>
-    <mergeCell ref="C37:F37"/>
-    <mergeCell ref="C38:F38"/>
-    <mergeCell ref="C39:F39"/>
-    <mergeCell ref="C40:F40"/>
+    <mergeCell ref="C34:F34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5304,7 +5116,7 @@
   <sheetData>
     <row r="2" spans="2:9">
       <c r="B2" s="1" t="s">
-        <v>148</v>
+        <v>132</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -5316,28 +5128,28 @@
     </row>
     <row r="4" spans="2:9" ht="35" customHeight="1">
       <c r="B4" s="14" t="s">
-        <v>149</v>
+        <v>133</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>152</v>
+        <v>136</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>153</v>
+        <v>137</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>154</v>
+        <v>138</v>
       </c>
       <c r="H4" s="14" t="s">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="I4" s="14" t="s">
-        <v>156</v>
+        <v>140</v>
       </c>
     </row>
     <row r="5" spans="2:9">
@@ -5345,25 +5157,25 @@
         <v>1</v>
       </c>
       <c r="C5" s="15">
-        <v>89066</v>
+        <v>89067</v>
       </c>
       <c r="D5" s="12">
         <v>0.5374104656196147</v>
       </c>
       <c r="E5" s="16">
-        <v>276719</v>
+        <v>276723</v>
       </c>
       <c r="F5" s="15">
-        <v>76666</v>
+        <v>76667</v>
       </c>
       <c r="G5" s="12">
         <v>0.4625895343803854</v>
       </c>
       <c r="H5" s="16">
-        <v>274837</v>
+        <v>274842</v>
       </c>
       <c r="I5" s="15">
-        <v>165731</v>
+        <v>165734</v>
       </c>
     </row>
     <row r="6" spans="2:9">
@@ -5371,25 +5183,25 @@
         <v>2</v>
       </c>
       <c r="C6" s="18">
-        <v>139415</v>
+        <v>139420</v>
       </c>
       <c r="D6" s="19">
         <v>0.5357376192342873</v>
       </c>
       <c r="E6" s="20">
-        <v>432051</v>
+        <v>432065</v>
       </c>
       <c r="F6" s="18">
-        <v>120815</v>
+        <v>120819</v>
       </c>
       <c r="G6" s="19">
         <v>0.4642623807657128</v>
       </c>
       <c r="H6" s="20">
-        <v>432011</v>
+        <v>432024</v>
       </c>
       <c r="I6" s="18">
-        <v>260230</v>
+        <v>260238</v>
       </c>
     </row>
     <row r="7" spans="2:9">
@@ -5397,25 +5209,25 @@
         <v>3</v>
       </c>
       <c r="C7" s="15">
-        <v>176821</v>
+        <v>176829</v>
       </c>
       <c r="D7" s="12">
         <v>0.5340650187412724</v>
       </c>
       <c r="E7" s="16">
-        <v>546585</v>
+        <v>546608</v>
       </c>
       <c r="F7" s="15">
-        <v>154264</v>
+        <v>154271</v>
       </c>
       <c r="G7" s="12">
         <v>0.4659349812587275</v>
       </c>
       <c r="H7" s="16">
-        <v>550220</v>
+        <v>550243</v>
       </c>
       <c r="I7" s="15">
-        <v>331086</v>
+        <v>331100</v>
       </c>
     </row>
     <row r="8" spans="2:9">
@@ -5423,25 +5235,25 @@
         <v>4</v>
       </c>
       <c r="C8" s="18">
-        <v>231928</v>
+        <v>231939</v>
       </c>
       <c r="D8" s="19">
         <v>0.5323926640863587</v>
       </c>
       <c r="E8" s="20">
-        <v>715111</v>
+        <v>715147</v>
       </c>
       <c r="F8" s="18">
-        <v>203705</v>
+        <v>203715</v>
       </c>
       <c r="G8" s="19">
         <v>0.4676073359136413</v>
       </c>
       <c r="H8" s="20">
-        <v>724721</v>
+        <v>724757</v>
       </c>
       <c r="I8" s="18">
-        <v>435633</v>
+        <v>435655</v>
       </c>
     </row>
     <row r="9" spans="2:9">
@@ -5449,25 +5261,25 @@
         <v>5</v>
       </c>
       <c r="C9" s="15">
-        <v>313561</v>
+        <v>313578</v>
       </c>
       <c r="D9" s="12">
         <v>0.5307205552153501</v>
       </c>
       <c r="E9" s="16">
-        <v>964362</v>
+        <v>964415</v>
       </c>
       <c r="F9" s="15">
-        <v>277260</v>
+        <v>277275</v>
       </c>
       <c r="G9" s="12">
         <v>0.4692794447846498</v>
       </c>
       <c r="H9" s="16">
-        <v>983906</v>
+        <v>983960</v>
       </c>
       <c r="I9" s="15">
-        <v>590821</v>
+        <v>590853</v>
       </c>
     </row>
     <row r="10" spans="2:9">
@@ -5475,25 +5287,25 @@
         <v>6</v>
       </c>
       <c r="C10" s="18">
-        <v>414109</v>
+        <v>414132</v>
       </c>
       <c r="D10" s="19">
         <v>0.5290486920740669</v>
       </c>
       <c r="E10" s="20">
-        <v>1270371</v>
+        <v>1270442</v>
       </c>
       <c r="F10" s="18">
-        <v>368634</v>
+        <v>368654</v>
       </c>
       <c r="G10" s="19">
         <v>0.4709513079259331</v>
       </c>
       <c r="H10" s="20">
-        <v>1304845</v>
+        <v>1304918</v>
       </c>
       <c r="I10" s="18">
-        <v>782743</v>
+        <v>782786</v>
       </c>
     </row>
     <row r="11" spans="2:9">
@@ -5501,25 +5313,25 @@
         <v>7</v>
       </c>
       <c r="C11" s="15">
-        <v>486946</v>
+        <v>486972</v>
       </c>
       <c r="D11" s="12">
         <v>0.5273770746083449</v>
       </c>
       <c r="E11" s="16">
-        <v>1490027</v>
+        <v>1490108</v>
       </c>
       <c r="F11" s="15">
-        <v>436389</v>
+        <v>436413</v>
       </c>
       <c r="G11" s="12">
         <v>0.472622925391655</v>
       </c>
       <c r="H11" s="16">
-        <v>1540762</v>
+        <v>1540846</v>
       </c>
       <c r="I11" s="15">
-        <v>923335</v>
+        <v>923385</v>
       </c>
     </row>
     <row r="12" spans="2:9">
@@ -5527,25 +5339,25 @@
         <v>8</v>
       </c>
       <c r="C12" s="18">
-        <v>556364</v>
+        <v>556391</v>
       </c>
       <c r="D12" s="19">
         <v>0.5257057027640366</v>
       </c>
       <c r="E12" s="20">
-        <v>1698127</v>
+        <v>1698211</v>
       </c>
       <c r="F12" s="18">
-        <v>501954</v>
+        <v>501979</v>
       </c>
       <c r="G12" s="19">
         <v>0.4742942972359634</v>
       </c>
       <c r="H12" s="20">
-        <v>1767759</v>
+        <v>1767847</v>
       </c>
       <c r="I12" s="18">
-        <v>1058318</v>
+        <v>1058370</v>
       </c>
     </row>
     <row r="13" spans="2:9">
@@ -5553,25 +5365,25 @@
         <v>9</v>
       </c>
       <c r="C13" s="15">
-        <v>616990</v>
+        <v>617016</v>
       </c>
       <c r="D13" s="12">
         <v>0.5240345764870094</v>
       </c>
       <c r="E13" s="16">
-        <v>1878397</v>
+        <v>1878475</v>
       </c>
       <c r="F13" s="15">
-        <v>560394</v>
+        <v>560418</v>
       </c>
       <c r="G13" s="12">
         <v>0.4759654235129906</v>
       </c>
       <c r="H13" s="16">
-        <v>1968569</v>
+        <v>1968651</v>
       </c>
       <c r="I13" s="15">
-        <v>1177385</v>
+        <v>1177434</v>
       </c>
     </row>
     <row r="14" spans="2:9">
@@ -5579,25 +5391,25 @@
         <v>10</v>
       </c>
       <c r="C14" s="18">
-        <v>700626</v>
+        <v>700647</v>
       </c>
       <c r="D14" s="19">
         <v>0.5223636957231473</v>
       </c>
       <c r="E14" s="20">
-        <v>2127613</v>
+        <v>2127678</v>
       </c>
       <c r="F14" s="18">
-        <v>640635</v>
+        <v>640654</v>
       </c>
       <c r="G14" s="19">
         <v>0.4776363042768528</v>
       </c>
       <c r="H14" s="20">
-        <v>2244734</v>
+        <v>2244803</v>
       </c>
       <c r="I14" s="18">
-        <v>1341260</v>
+        <v>1341301</v>
       </c>
     </row>
     <row r="15" spans="2:9">
@@ -5605,25 +5417,25 @@
         <v>11</v>
       </c>
       <c r="C15" s="15">
-        <v>776030</v>
+        <v>776043</v>
       </c>
       <c r="D15" s="12">
         <v>0.5206930604183501</v>
       </c>
       <c r="E15" s="16">
-        <v>2350621</v>
+        <v>2350660</v>
       </c>
       <c r="F15" s="15">
-        <v>714349</v>
+        <v>714361</v>
       </c>
       <c r="G15" s="12">
         <v>0.47930693958165</v>
       </c>
       <c r="H15" s="16">
-        <v>2496677</v>
+        <v>2496719</v>
       </c>
       <c r="I15" s="15">
-        <v>1490378</v>
+        <v>1490403</v>
       </c>
     </row>
     <row r="16" spans="2:9">
@@ -5657,25 +5469,25 @@
         <v>13</v>
       </c>
       <c r="C17" s="15">
-        <v>848095</v>
+        <v>848079</v>
       </c>
       <c r="D17" s="12">
         <v>0.517352525969628</v>
       </c>
       <c r="E17" s="16">
-        <v>2555902</v>
+        <v>2555852</v>
       </c>
       <c r="F17" s="15">
-        <v>791203</v>
+        <v>791188</v>
       </c>
       <c r="G17" s="12">
         <v>0.482647474030372</v>
       </c>
       <c r="H17" s="16">
-        <v>2751285</v>
+        <v>2751231</v>
       </c>
       <c r="I17" s="15">
-        <v>1639299</v>
+        <v>1639267</v>
       </c>
     </row>
     <row r="18" spans="2:9">
@@ -5683,25 +5495,25 @@
         <v>14</v>
       </c>
       <c r="C18" s="18">
-        <v>1033452</v>
+        <v>1033408</v>
       </c>
       <c r="D18" s="19">
         <v>0.5156826267175821</v>
       </c>
       <c r="E18" s="20">
-        <v>3106616</v>
+        <v>3106483</v>
       </c>
       <c r="F18" s="18">
-        <v>970595</v>
+        <v>970553</v>
       </c>
       <c r="G18" s="19">
         <v>0.4843173732824178</v>
       </c>
       <c r="H18" s="20">
-        <v>3366534</v>
+        <v>3366390</v>
       </c>
       <c r="I18" s="18">
-        <v>2004047</v>
+        <v>2003961</v>
       </c>
     </row>
     <row r="19" spans="2:9">
@@ -5709,25 +5521,25 @@
         <v>15</v>
       </c>
       <c r="C19" s="15">
-        <v>1019570</v>
+        <v>1019501</v>
       </c>
       <c r="D19" s="12">
         <v>0.5140129727083589</v>
       </c>
       <c r="E19" s="16">
-        <v>3057116</v>
+        <v>3056908</v>
       </c>
       <c r="F19" s="15">
-        <v>963979</v>
+        <v>963914</v>
       </c>
       <c r="G19" s="12">
         <v>0.4859870272916412</v>
       </c>
       <c r="H19" s="16">
-        <v>3335112</v>
+        <v>3334885</v>
       </c>
       <c r="I19" s="15">
-        <v>1983550</v>
+        <v>1983414</v>
       </c>
     </row>
     <row r="20" spans="2:9">
@@ -5735,25 +5547,25 @@
         <v>16</v>
       </c>
       <c r="C20" s="18">
-        <v>1045460</v>
+        <v>1045359</v>
       </c>
       <c r="D20" s="19">
         <v>0.5123435638879371</v>
       </c>
       <c r="E20" s="20">
-        <v>3126798</v>
+        <v>3126495</v>
       </c>
       <c r="F20" s="18">
-        <v>995085</v>
+        <v>994988</v>
       </c>
       <c r="G20" s="19">
         <v>0.4876564361120628</v>
       </c>
       <c r="H20" s="20">
-        <v>3434000</v>
+        <v>3433669</v>
       </c>
       <c r="I20" s="18">
-        <v>2040544</v>
+        <v>2040347</v>
       </c>
     </row>
     <row r="21" spans="2:9">
@@ -5761,25 +5573,25 @@
         <v>17</v>
       </c>
       <c r="C21" s="15">
-        <v>1116533</v>
+        <v>1116390</v>
       </c>
       <c r="D21" s="12">
         <v>0.5106744002023119</v>
       </c>
       <c r="E21" s="16">
-        <v>3330902</v>
+        <v>3330475</v>
       </c>
       <c r="F21" s="15">
-        <v>1069857</v>
+        <v>1069719</v>
       </c>
       <c r="G21" s="12">
         <v>0.489325599797688</v>
       </c>
       <c r="H21" s="16">
-        <v>3682676</v>
+        <v>3682205</v>
       </c>
       <c r="I21" s="15">
-        <v>2186390</v>
+        <v>2186110</v>
       </c>
     </row>
     <row r="22" spans="2:9">
@@ -5787,25 +5599,25 @@
         <v>18</v>
       </c>
       <c r="C22" s="18">
-        <v>1183463</v>
+        <v>1183270</v>
       </c>
       <c r="D22" s="19">
         <v>0.5090054815974943</v>
       </c>
       <c r="E22" s="20">
-        <v>3521619</v>
+        <v>3521046</v>
       </c>
       <c r="F22" s="18">
-        <v>1141586</v>
+        <v>1141401</v>
       </c>
       <c r="G22" s="19">
         <v>0.4909945184025059</v>
       </c>
       <c r="H22" s="20">
-        <v>3919624</v>
+        <v>3918987</v>
       </c>
       <c r="I22" s="18">
-        <v>2325049</v>
+        <v>2324671</v>
       </c>
     </row>
     <row r="23" spans="2:9">
@@ -5813,25 +5625,25 @@
         <v>19</v>
       </c>
       <c r="C23" s="15">
-        <v>1140655</v>
+        <v>1140428</v>
       </c>
       <c r="D23" s="12">
         <v>0.5073368080195105</v>
       </c>
       <c r="E23" s="16">
-        <v>3385633</v>
+        <v>3384958</v>
       </c>
       <c r="F23" s="15">
-        <v>1107664</v>
+        <v>1107443</v>
       </c>
       <c r="G23" s="12">
         <v>0.4926631919804895</v>
       </c>
       <c r="H23" s="16">
-        <v>3793512</v>
+        <v>3792756</v>
       </c>
       <c r="I23" s="15">
-        <v>2248320</v>
+        <v>2247871</v>
       </c>
     </row>
     <row r="24" spans="2:9">
@@ -5839,25 +5651,25 @@
         <v>20</v>
       </c>
       <c r="C24" s="18">
-        <v>1093877</v>
+        <v>1093616</v>
       </c>
       <c r="D24" s="19">
         <v>0.5056683794144035</v>
       </c>
       <c r="E24" s="20">
-        <v>3238558</v>
+        <v>3237784</v>
       </c>
       <c r="F24" s="18">
-        <v>1069353</v>
+        <v>1069098</v>
       </c>
       <c r="G24" s="19">
         <v>0.4943316205855967</v>
       </c>
       <c r="H24" s="20">
-        <v>3653021</v>
+        <v>3652148</v>
       </c>
       <c r="I24" s="18">
-        <v>2163231</v>
+        <v>2162714</v>
       </c>
     </row>
     <row r="25" spans="2:9">
@@ -5865,25 +5677,25 @@
         <v>21</v>
       </c>
       <c r="C25" s="15">
-        <v>1044323</v>
+        <v>1044029</v>
       </c>
       <c r="D25" s="12">
         <v>0.5040001957282314</v>
       </c>
       <c r="E25" s="16">
-        <v>3084008</v>
+        <v>3083141</v>
       </c>
       <c r="F25" s="15">
-        <v>1027746</v>
+        <v>1027457</v>
       </c>
       <c r="G25" s="12">
         <v>0.4959998042717687</v>
       </c>
       <c r="H25" s="16">
-        <v>3501985</v>
+        <v>3501000</v>
       </c>
       <c r="I25" s="15">
-        <v>2072069</v>
+        <v>2071486</v>
       </c>
     </row>
     <row r="26" spans="2:9">
@@ -5891,25 +5703,25 @@
         <v>22</v>
       </c>
       <c r="C26" s="18">
-        <v>1046537</v>
+        <v>1046195</v>
       </c>
       <c r="D26" s="19">
         <v>0.5023322569070686</v>
       </c>
       <c r="E26" s="20">
-        <v>3082711</v>
+        <v>3081704</v>
       </c>
       <c r="F26" s="18">
-        <v>1036819</v>
+        <v>1036480</v>
       </c>
       <c r="G26" s="19">
         <v>0.4976677430929314</v>
       </c>
       <c r="H26" s="20">
-        <v>3523945</v>
+        <v>3522794</v>
       </c>
       <c r="I26" s="18">
-        <v>2083356</v>
+        <v>2082675</v>
       </c>
     </row>
     <row r="27" spans="2:9">
@@ -5917,25 +5729,25 @@
         <v>23</v>
       </c>
       <c r="C27" s="15">
-        <v>1047539</v>
+        <v>1047146</v>
       </c>
       <c r="D27" s="12">
         <v>0.5006645628970051</v>
       </c>
       <c r="E27" s="16">
-        <v>3077841</v>
+        <v>3076688</v>
       </c>
       <c r="F27" s="15">
-        <v>1044758</v>
+        <v>1044367</v>
       </c>
       <c r="G27" s="12">
         <v>0.499335437102995</v>
       </c>
       <c r="H27" s="16">
-        <v>3541927</v>
+        <v>3540600</v>
       </c>
       <c r="I27" s="15">
-        <v>2092297</v>
+        <v>2091513</v>
       </c>
     </row>
     <row r="28" spans="2:9">
@@ -5943,25 +5755,25 @@
         <v>24</v>
       </c>
       <c r="C28" s="18">
-        <v>1101349</v>
+        <v>1100880</v>
       </c>
       <c r="D28" s="19">
         <v>0.4989971136441465</v>
       </c>
       <c r="E28" s="20">
-        <v>3227741</v>
+        <v>3226365</v>
       </c>
       <c r="F28" s="18">
-        <v>1105776</v>
+        <v>1105305</v>
       </c>
       <c r="G28" s="19">
         <v>0.5010028863558533</v>
       </c>
       <c r="H28" s="20">
-        <v>3739286</v>
+        <v>3737693</v>
       </c>
       <c r="I28" s="18">
-        <v>2207125</v>
+        <v>2206185</v>
       </c>
     </row>
     <row r="29" spans="2:9">
@@ -5969,25 +5781,25 @@
         <v>25</v>
       </c>
       <c r="C29" s="15">
-        <v>993449</v>
+        <v>992974</v>
       </c>
       <c r="D29" s="12">
         <v>0.4973299090946151</v>
       </c>
       <c r="E29" s="16">
-        <v>2904137</v>
+        <v>2902747</v>
       </c>
       <c r="F29" s="15">
-        <v>1004117</v>
+        <v>1003636</v>
       </c>
       <c r="G29" s="12">
         <v>0.5026700909053851</v>
       </c>
       <c r="H29" s="16">
-        <v>3386908</v>
+        <v>3385288</v>
       </c>
       <c r="I29" s="15">
-        <v>1997566</v>
+        <v>1996611</v>
       </c>
     </row>
     <row r="30" spans="2:9">
@@ -5995,25 +5807,25 @@
         <v>26</v>
       </c>
       <c r="C30" s="18">
-        <v>1153286</v>
+        <v>1152667</v>
       </c>
       <c r="D30" s="19">
         <v>0.4956629491945477</v>
       </c>
       <c r="E30" s="20">
-        <v>3362838</v>
+        <v>3361033</v>
       </c>
       <c r="F30" s="18">
-        <v>1173468</v>
+        <v>1172839</v>
       </c>
       <c r="G30" s="19">
         <v>0.5043370508054522</v>
       </c>
       <c r="H30" s="20">
-        <v>3948101</v>
+        <v>3945982</v>
       </c>
       <c r="I30" s="18">
-        <v>2326754</v>
+        <v>2325506</v>
       </c>
     </row>
     <row r="31" spans="2:9">
@@ -6021,25 +5833,25 @@
         <v>27</v>
       </c>
       <c r="C31" s="15">
-        <v>1098239</v>
+        <v>1097585</v>
       </c>
       <c r="D31" s="12">
         <v>0.4939962338900981</v>
       </c>
       <c r="E31" s="16">
-        <v>3194209</v>
+        <v>3192308</v>
       </c>
       <c r="F31" s="15">
-        <v>1124934</v>
+        <v>1124264</v>
       </c>
       <c r="G31" s="12">
         <v>0.5060037661099018</v>
       </c>
       <c r="H31" s="16">
-        <v>3775212</v>
+        <v>3772965</v>
       </c>
       <c r="I31" s="15">
-        <v>2223172</v>
+        <v>2221849</v>
       </c>
     </row>
     <row r="32" spans="2:9">
@@ -6047,25 +5859,25 @@
         <v>28</v>
       </c>
       <c r="C32" s="18">
-        <v>1096521</v>
+        <v>1095800</v>
       </c>
       <c r="D32" s="19">
         <v>0.4923297631274352</v>
       </c>
       <c r="E32" s="20">
-        <v>3181127</v>
+        <v>3179038</v>
       </c>
       <c r="F32" s="18">
-        <v>1130687</v>
+        <v>1129944</v>
       </c>
       <c r="G32" s="19">
         <v>0.5076702368725649</v>
       </c>
       <c r="H32" s="20">
-        <v>3784902</v>
+        <v>3782415</v>
       </c>
       <c r="I32" s="18">
-        <v>2227208</v>
+        <v>2225745</v>
       </c>
     </row>
     <row r="33" spans="2:9">
@@ -6073,25 +5885,25 @@
         <v>29</v>
       </c>
       <c r="C33" s="15">
-        <v>1147941</v>
+        <v>1147112</v>
       </c>
       <c r="D33" s="12">
         <v>0.4906635368527438</v>
       </c>
       <c r="E33" s="16">
-        <v>3321861</v>
+        <v>3319462</v>
       </c>
       <c r="F33" s="15">
-        <v>1191628</v>
+        <v>1190767</v>
       </c>
       <c r="G33" s="12">
         <v>0.509336463147256</v>
       </c>
       <c r="H33" s="16">
-        <v>3978784</v>
+        <v>3975910</v>
       </c>
       <c r="I33" s="15">
-        <v>2339569</v>
+        <v>2337879</v>
       </c>
     </row>
     <row r="34" spans="2:9">
@@ -6099,25 +5911,25 @@
         <v>30</v>
       </c>
       <c r="C34" s="18">
-        <v>1199009</v>
+        <v>1198062</v>
       </c>
       <c r="D34" s="19">
         <v>0.488997555012225</v>
       </c>
       <c r="E34" s="20">
-        <v>3460845</v>
+        <v>3458109</v>
       </c>
       <c r="F34" s="18">
-        <v>1252965</v>
+        <v>1251975</v>
       </c>
       <c r="G34" s="19">
         <v>0.511002444987775</v>
       </c>
       <c r="H34" s="20">
-        <v>4172980</v>
+        <v>4169682</v>
       </c>
       <c r="I34" s="18">
-        <v>2451974</v>
+        <v>2450036</v>
       </c>
     </row>
     <row r="35" spans="2:9">
@@ -6125,25 +5937,25 @@
         <v>31</v>
       </c>
       <c r="C35" s="15">
-        <v>1143496</v>
+        <v>1142513</v>
       </c>
       <c r="D35" s="12">
         <v>0.4873318175520948</v>
       </c>
       <c r="E35" s="16">
-        <v>3292241</v>
+        <v>3289412</v>
       </c>
       <c r="F35" s="15">
-        <v>1202946</v>
+        <v>1201912</v>
       </c>
       <c r="G35" s="12">
         <v>0.5126681824479052</v>
       </c>
       <c r="H35" s="16">
-        <v>3996236</v>
+        <v>3992802</v>
       </c>
       <c r="I35" s="15">
-        <v>2346442</v>
+        <v>2344425</v>
       </c>
     </row>
     <row r="36" spans="2:9">
@@ -6151,25 +5963,25 @@
         <v>32</v>
       </c>
       <c r="C36" s="18">
-        <v>1088115</v>
+        <v>1087102</v>
       </c>
       <c r="D36" s="19">
         <v>0.4856663244185857</v>
       </c>
       <c r="E36" s="20">
-        <v>3124852</v>
+        <v>3121944</v>
       </c>
       <c r="F36" s="18">
-        <v>1152343</v>
+        <v>1151270</v>
       </c>
       <c r="G36" s="19">
         <v>0.5143336755814142</v>
       </c>
       <c r="H36" s="20">
-        <v>3818426</v>
+        <v>3814872</v>
       </c>
       <c r="I36" s="18">
-        <v>2240457</v>
+        <v>2238372</v>
       </c>
     </row>
     <row r="37" spans="2:9">
@@ -6177,25 +5989,25 @@
         <v>33</v>
       </c>
       <c r="C37" s="15">
-        <v>1032896</v>
+        <v>1031858</v>
       </c>
       <c r="D37" s="12">
         <v>0.4840010755579457</v>
       </c>
       <c r="E37" s="16">
-        <v>2958754</v>
+        <v>2955782</v>
       </c>
       <c r="F37" s="15">
-        <v>1101181</v>
+        <v>1100075</v>
       </c>
       <c r="G37" s="12">
         <v>0.5159989244420543</v>
       </c>
       <c r="H37" s="16">
-        <v>3639647</v>
+        <v>3635991</v>
       </c>
       <c r="I37" s="15">
-        <v>2134077</v>
+        <v>2131934</v>
       </c>
     </row>
     <row r="38" spans="2:9">
@@ -6203,25 +6015,25 @@
         <v>34</v>
       </c>
       <c r="C38" s="18">
-        <v>1030647</v>
+        <v>1029532</v>
       </c>
       <c r="D38" s="19">
         <v>0.4823360709164385</v>
       </c>
       <c r="E38" s="20">
-        <v>2944830</v>
+        <v>2941644</v>
       </c>
       <c r="F38" s="18">
-        <v>1106135</v>
+        <v>1104939</v>
       </c>
       <c r="G38" s="19">
         <v>0.5176639290835614</v>
       </c>
       <c r="H38" s="20">
-        <v>3646752</v>
+        <v>3642807</v>
       </c>
       <c r="I38" s="18">
-        <v>2136783</v>
+        <v>2134471</v>
       </c>
     </row>
     <row r="39" spans="2:9">
@@ -6229,25 +6041,25 @@
         <v>35</v>
       </c>
       <c r="C39" s="15">
-        <v>1028364</v>
+        <v>1027169</v>
       </c>
       <c r="D39" s="12">
         <v>0.4806713104403438</v>
       </c>
       <c r="E39" s="16">
-        <v>2930857</v>
+        <v>2927451</v>
       </c>
       <c r="F39" s="15">
-        <v>1111069</v>
+        <v>1109778</v>
       </c>
       <c r="G39" s="12">
         <v>0.5193286895596562</v>
       </c>
       <c r="H39" s="16">
-        <v>3653731</v>
+        <v>3649486</v>
       </c>
       <c r="I39" s="15">
-        <v>2139433</v>
+        <v>2136947</v>
       </c>
     </row>
     <row r="40" spans="2:9">
@@ -6255,25 +6067,25 @@
         <v>36</v>
       </c>
       <c r="C40" s="18">
-        <v>1078607</v>
+        <v>1077263</v>
       </c>
       <c r="D40" s="19">
         <v>0.4790067940759568</v>
       </c>
       <c r="E40" s="20">
-        <v>3066257</v>
+        <v>3062436</v>
       </c>
       <c r="F40" s="18">
-        <v>1173150</v>
+        <v>1171688</v>
       </c>
       <c r="G40" s="19">
         <v>0.5209932059240431</v>
       </c>
       <c r="H40" s="20">
-        <v>3848104</v>
+        <v>3843308</v>
       </c>
       <c r="I40" s="18">
-        <v>2251757</v>
+        <v>2248951</v>
       </c>
     </row>
     <row r="41" spans="2:9">
@@ -6281,25 +6093,25 @@
         <v>37</v>
       </c>
       <c r="C41" s="15">
-        <v>971283</v>
+        <v>969993</v>
       </c>
       <c r="D41" s="12">
         <v>0.4773425217695886</v>
       </c>
       <c r="E41" s="16">
-        <v>2754158</v>
+        <v>2750501</v>
       </c>
       <c r="F41" s="15">
-        <v>1063489</v>
+        <v>1062077</v>
       </c>
       <c r="G41" s="12">
         <v>0.5226574782304114</v>
       </c>
       <c r="H41" s="16">
-        <v>3479556</v>
+        <v>3474936</v>
       </c>
       <c r="I41" s="15">
-        <v>2034772</v>
+        <v>2032070</v>
       </c>
     </row>
     <row r="42" spans="2:9">
@@ -6307,25 +6119,25 @@
         <v>38</v>
       </c>
       <c r="C42" s="18">
-        <v>1125999</v>
+        <v>1124399</v>
       </c>
       <c r="D42" s="19">
         <v>0.475678493467566</v>
       </c>
       <c r="E42" s="20">
-        <v>3184774</v>
+        <v>3180248</v>
       </c>
       <c r="F42" s="18">
-        <v>1241144</v>
+        <v>1239380</v>
       </c>
       <c r="G42" s="19">
         <v>0.5243215065324341</v>
       </c>
       <c r="H42" s="20">
-        <v>4050519</v>
+        <v>4044762</v>
       </c>
       <c r="I42" s="18">
-        <v>2367143</v>
+        <v>2363778</v>
       </c>
     </row>
     <row r="43" spans="2:9">
@@ -6333,25 +6145,25 @@
         <v>39</v>
       </c>
       <c r="C43" s="15">
-        <v>1071194</v>
+        <v>1069577</v>
       </c>
       <c r="D43" s="12">
         <v>0.4740147091162314</v>
       </c>
       <c r="E43" s="16">
-        <v>3022084</v>
+        <v>3017522</v>
       </c>
       <c r="F43" s="15">
-        <v>1188639</v>
+        <v>1186845</v>
       </c>
       <c r="G43" s="12">
         <v>0.5259852908837687</v>
       </c>
       <c r="H43" s="16">
-        <v>3869334</v>
+        <v>3863492</v>
       </c>
       <c r="I43" s="15">
-        <v>2259834</v>
+        <v>2256422</v>
       </c>
     </row>
     <row r="44" spans="2:9">
@@ -6359,25 +6171,25 @@
         <v>40</v>
       </c>
       <c r="C44" s="18">
-        <v>1068692</v>
+        <v>1066979</v>
       </c>
       <c r="D44" s="19">
         <v>0.4723511686619432</v>
       </c>
       <c r="E44" s="20">
-        <v>3007381</v>
+        <v>3002561</v>
       </c>
       <c r="F44" s="18">
-        <v>1193803</v>
+        <v>1191889</v>
       </c>
       <c r="G44" s="19">
         <v>0.5276488313380568</v>
       </c>
       <c r="H44" s="20">
-        <v>3876291</v>
+        <v>3870078</v>
       </c>
       <c r="I44" s="18">
-        <v>2262494</v>
+        <v>2258868</v>
       </c>
     </row>
     <row r="45" spans="2:9">
@@ -6385,25 +6197,25 @@
         <v>41</v>
       </c>
       <c r="C45" s="15">
-        <v>1118131</v>
+        <v>1116230</v>
       </c>
       <c r="D45" s="12">
         <v>0.4706878720510754</v>
       </c>
       <c r="E45" s="16">
-        <v>3138530</v>
+        <v>3133194</v>
       </c>
       <c r="F45" s="15">
-        <v>1257394</v>
+        <v>1255257</v>
       </c>
       <c r="G45" s="12">
         <v>0.5293121279489247</v>
       </c>
       <c r="H45" s="16">
-        <v>4072424</v>
+        <v>4065501</v>
       </c>
       <c r="I45" s="15">
-        <v>2375525</v>
+        <v>2371487</v>
       </c>
     </row>
     <row r="46" spans="2:9">
@@ -6411,25 +6223,25 @@
         <v>42</v>
       </c>
       <c r="C46" s="18">
-        <v>1167315</v>
+        <v>1165214</v>
       </c>
       <c r="D46" s="19">
         <v>0.4690248192300176</v>
       </c>
       <c r="E46" s="20">
-        <v>3268281</v>
+        <v>3262398</v>
       </c>
       <c r="F46" s="18">
-        <v>1321498</v>
+        <v>1319119</v>
       </c>
       <c r="G46" s="19">
         <v>0.5309751807699824</v>
       </c>
       <c r="H46" s="20">
-        <v>4269192</v>
+        <v>4261507</v>
       </c>
       <c r="I46" s="18">
-        <v>2488813</v>
+        <v>2484333</v>
       </c>
     </row>
     <row r="47" spans="2:9">
@@ -6437,25 +6249,25 @@
         <v>43</v>
       </c>
       <c r="C47" s="15">
-        <v>1112823</v>
+        <v>1110711</v>
       </c>
       <c r="D47" s="12">
         <v>0.4673620101451754</v>
       </c>
       <c r="E47" s="16">
-        <v>3107814</v>
+        <v>3101915</v>
       </c>
       <c r="F47" s="15">
-        <v>1268250</v>
+        <v>1265843</v>
       </c>
       <c r="G47" s="12">
         <v>0.5326379898548247</v>
       </c>
       <c r="H47" s="16">
-        <v>4086784</v>
+        <v>4079026</v>
       </c>
       <c r="I47" s="15">
-        <v>2381073</v>
+        <v>2376553</v>
       </c>
     </row>
     <row r="48" spans="2:9">
@@ -6463,25 +6275,25 @@
         <v>44</v>
       </c>
       <c r="C48" s="18">
-        <v>1058566</v>
+        <v>1056450</v>
       </c>
       <c r="D48" s="19">
         <v>0.4656994447429698</v>
       </c>
       <c r="E48" s="20">
-        <v>2948794</v>
+        <v>2942900</v>
       </c>
       <c r="F48" s="18">
-        <v>1214501</v>
+        <v>1212073</v>
       </c>
       <c r="G48" s="19">
         <v>0.5343005552570302</v>
       </c>
       <c r="H48" s="20">
-        <v>3903662</v>
+        <v>3895860</v>
       </c>
       <c r="I48" s="18">
-        <v>2273067</v>
+        <v>2268523</v>
       </c>
     </row>
     <row r="49" spans="2:9">
@@ -6489,25 +6301,25 @@
         <v>45</v>
       </c>
       <c r="C49" s="15">
-        <v>1004545</v>
+        <v>1002434</v>
       </c>
       <c r="D49" s="12">
         <v>0.4640371229698376</v>
       </c>
       <c r="E49" s="16">
-        <v>2791216</v>
+        <v>2785352</v>
       </c>
       <c r="F49" s="15">
-        <v>1160249</v>
+        <v>1157811</v>
       </c>
       <c r="G49" s="12">
         <v>0.5359628770301624</v>
       </c>
       <c r="H49" s="16">
-        <v>3719832</v>
+        <v>3712017</v>
       </c>
       <c r="I49" s="15">
-        <v>2164794</v>
+        <v>2160246</v>
       </c>
     </row>
     <row r="50" spans="2:9">
@@ -6515,25 +6327,25 @@
         <v>46</v>
       </c>
       <c r="C50" s="18">
-        <v>1002103</v>
+        <v>999889</v>
       </c>
       <c r="D50" s="19">
         <v>0.4623750447722315</v>
       </c>
       <c r="E50" s="20">
-        <v>2777372</v>
+        <v>2771238</v>
       </c>
       <c r="F50" s="18">
-        <v>1165191</v>
+        <v>1162618</v>
       </c>
       <c r="G50" s="19">
         <v>0.5376249552277685</v>
       </c>
       <c r="H50" s="20">
-        <v>3726207</v>
+        <v>3717977</v>
       </c>
       <c r="I50" s="18">
-        <v>2167294</v>
+        <v>2162507</v>
       </c>
     </row>
     <row r="51" spans="2:9">
@@ -6541,25 +6353,25 @@
         <v>47</v>
       </c>
       <c r="C51" s="15">
-        <v>999652</v>
+        <v>997334</v>
       </c>
       <c r="D51" s="12">
         <v>0.4607132100966195</v>
       </c>
       <c r="E51" s="16">
-        <v>2763556</v>
+        <v>2757149</v>
       </c>
       <c r="F51" s="15">
-        <v>1170140</v>
+        <v>1167428</v>
       </c>
       <c r="G51" s="12">
         <v>0.5392867899033804</v>
       </c>
       <c r="H51" s="16">
-        <v>3732547</v>
+        <v>3723894</v>
       </c>
       <c r="I51" s="15">
-        <v>2169792</v>
+        <v>2164762</v>
       </c>
     </row>
     <row r="52" spans="2:9">
@@ -6567,25 +6379,25 @@
         <v>48</v>
       </c>
       <c r="C52" s="18">
-        <v>1048285</v>
+        <v>1045734</v>
       </c>
       <c r="D52" s="19">
         <v>0.4590516188894858</v>
       </c>
       <c r="E52" s="20">
-        <v>2890657</v>
+        <v>2883622</v>
       </c>
       <c r="F52" s="18">
-        <v>1235304</v>
+        <v>1232298</v>
       </c>
       <c r="G52" s="19">
         <v>0.5409483811105142</v>
       </c>
       <c r="H52" s="20">
-        <v>3930419</v>
+        <v>3920853</v>
       </c>
       <c r="I52" s="18">
-        <v>2283589</v>
+        <v>2278032</v>
       </c>
     </row>
     <row r="53" spans="2:9">
@@ -6593,25 +6405,25 @@
         <v>49</v>
       </c>
       <c r="C53" s="15">
-        <v>943758</v>
+        <v>941360</v>
       </c>
       <c r="D53" s="12">
         <v>0.4573902710973297</v>
       </c>
       <c r="E53" s="16">
-        <v>2595826</v>
+        <v>2589229</v>
       </c>
       <c r="F53" s="15">
-        <v>1119596</v>
+        <v>1116751</v>
       </c>
       <c r="G53" s="12">
         <v>0.5426097289026702</v>
       </c>
       <c r="H53" s="16">
-        <v>3553236</v>
+        <v>3544207</v>
       </c>
       <c r="I53" s="15">
-        <v>2063355</v>
+        <v>2058111</v>
       </c>
     </row>
     <row r="54" spans="2:9">
@@ -6619,25 +6431,25 @@
         <v>50</v>
       </c>
       <c r="C54" s="18">
-        <v>1093935</v>
+        <v>1091016</v>
       </c>
       <c r="D54" s="19">
         <v>0.4557291666666667</v>
       </c>
       <c r="E54" s="20">
-        <v>3001262</v>
+        <v>2993253</v>
       </c>
       <c r="F54" s="18">
-        <v>1306471</v>
+        <v>1302985</v>
       </c>
       <c r="G54" s="19">
         <v>0.5442708333333333</v>
       </c>
       <c r="H54" s="20">
-        <v>4135805</v>
+        <v>4124769</v>
       </c>
       <c r="I54" s="18">
-        <v>2400406</v>
+        <v>2394001</v>
       </c>
     </row>
     <row r="55" spans="2:9">
@@ -6645,25 +6457,25 @@
         <v>51</v>
       </c>
       <c r="C55" s="15">
-        <v>1040484</v>
+        <v>1037587</v>
       </c>
       <c r="D55" s="12">
         <v>0.4540683055440276</v>
       </c>
       <c r="E55" s="16">
-        <v>2847380</v>
+        <v>2839451</v>
       </c>
       <c r="F55" s="15">
-        <v>1250986</v>
+        <v>1247503</v>
       </c>
       <c r="G55" s="12">
         <v>0.5459316944559724</v>
       </c>
       <c r="H55" s="16">
-        <v>3950122</v>
+        <v>3939122</v>
       </c>
       <c r="I55" s="15">
-        <v>2291470</v>
+        <v>2285089</v>
       </c>
     </row>
     <row r="56" spans="2:9">
@@ -6671,25 +6483,25 @@
         <v>52</v>
       </c>
       <c r="C56" s="18">
-        <v>1037867</v>
+        <v>1034850</v>
       </c>
       <c r="D56" s="19">
         <v>0.4524076876759589</v>
       </c>
       <c r="E56" s="20">
-        <v>2833018</v>
+        <v>2824784</v>
       </c>
       <c r="F56" s="18">
-        <v>1256230</v>
+        <v>1252579</v>
       </c>
       <c r="G56" s="19">
         <v>0.5475923123240409</v>
       </c>
       <c r="H56" s="20">
-        <v>3956622</v>
+        <v>3945123</v>
       </c>
       <c r="I56" s="18">
-        <v>2294096</v>
+        <v>2287429</v>
       </c>
     </row>
     <row r="57" spans="2:9">
@@ -6697,25 +6509,25 @@
         <v>53</v>
       </c>
       <c r="C57" s="15">
-        <v>1085705</v>
+        <v>1082411</v>
       </c>
       <c r="D57" s="12">
         <v>0.4507473130090231</v>
       </c>
       <c r="E57" s="16">
-        <v>2956088</v>
+        <v>2947119</v>
       </c>
       <c r="F57" s="15">
-        <v>1322973</v>
+        <v>1318959</v>
       </c>
       <c r="G57" s="12">
         <v>0.5492526869909768</v>
       </c>
       <c r="H57" s="16">
-        <v>4156275</v>
+        <v>4143665</v>
       </c>
       <c r="I57" s="15">
-        <v>2408678</v>
+        <v>2401371</v>
       </c>
     </row>
     <row r="58" spans="2:9">
@@ -6723,25 +6535,25 @@
         <v>54</v>
       </c>
       <c r="C58" s="18">
-        <v>1133282</v>
+        <v>1129696</v>
       </c>
       <c r="D58" s="19">
         <v>0.4490871814897979</v>
       </c>
       <c r="E58" s="20">
-        <v>3077803</v>
+        <v>3068066</v>
       </c>
       <c r="F58" s="18">
-        <v>1390241</v>
+        <v>1385843</v>
       </c>
       <c r="G58" s="19">
         <v>0.550912818510202</v>
       </c>
       <c r="H58" s="20">
-        <v>4356533</v>
+        <v>4342750</v>
       </c>
       <c r="I58" s="18">
-        <v>2523523</v>
+        <v>2515539</v>
       </c>
     </row>
     <row r="59" spans="2:9">
@@ -6749,25 +6561,25 @@
         <v>55</v>
       </c>
       <c r="C59" s="15">
-        <v>1080175</v>
+        <v>1076623</v>
       </c>
       <c r="D59" s="12">
         <v>0.447427293064877</v>
       </c>
       <c r="E59" s="16">
-        <v>2926139</v>
+        <v>2916515</v>
       </c>
       <c r="F59" s="15">
-        <v>1334017</v>
+        <v>1329629</v>
       </c>
       <c r="G59" s="12">
         <v>0.5525727069351229</v>
       </c>
       <c r="H59" s="16">
-        <v>4169748</v>
+        <v>4156034</v>
       </c>
       <c r="I59" s="15">
-        <v>2414192</v>
+        <v>2406252</v>
       </c>
     </row>
     <row r="60" spans="2:9">
@@ -6775,25 +6587,25 @@
         <v>56</v>
       </c>
       <c r="C60" s="18">
-        <v>1027316</v>
+        <v>1023806</v>
       </c>
       <c r="D60" s="19">
         <v>0.4457676476808694</v>
       </c>
       <c r="E60" s="20">
-        <v>2775889</v>
+        <v>2766407</v>
       </c>
       <c r="F60" s="18">
-        <v>1277283</v>
+        <v>1272920</v>
       </c>
       <c r="G60" s="19">
         <v>0.5542323523191305</v>
       </c>
       <c r="H60" s="20">
-        <v>3982294</v>
+        <v>3968692</v>
       </c>
       <c r="I60" s="18">
-        <v>2304599</v>
+        <v>2296727</v>
       </c>
     </row>
     <row r="61" spans="2:9">
@@ -6801,25 +6613,25 @@
         <v>57</v>
       </c>
       <c r="C61" s="15">
-        <v>974703</v>
+        <v>971249</v>
       </c>
       <c r="D61" s="12">
         <v>0.4441082452844001</v>
       </c>
       <c r="E61" s="16">
-        <v>2627050</v>
+        <v>2617739</v>
       </c>
       <c r="F61" s="15">
-        <v>1220039</v>
+        <v>1215715</v>
       </c>
       <c r="G61" s="12">
         <v>0.5558917547155998</v>
       </c>
       <c r="H61" s="16">
-        <v>3794178</v>
+        <v>3780731</v>
       </c>
       <c r="I61" s="15">
-        <v>2194743</v>
+        <v>2186964</v>
       </c>
     </row>
     <row r="62" spans="2:9">
@@ -6827,25 +6639,25 @@
         <v>58</v>
       </c>
       <c r="C62" s="18">
-        <v>972165</v>
+        <v>968589</v>
       </c>
       <c r="D62" s="19">
         <v>0.4424490858221095</v>
       </c>
       <c r="E62" s="20">
-        <v>2613567</v>
+        <v>2603951</v>
       </c>
       <c r="F62" s="18">
-        <v>1225071</v>
+        <v>1220564</v>
       </c>
       <c r="G62" s="19">
         <v>0.5575509141778905</v>
       </c>
       <c r="H62" s="20">
-        <v>3800168</v>
+        <v>3786187</v>
       </c>
       <c r="I62" s="18">
-        <v>2197237</v>
+        <v>2189153</v>
       </c>
     </row>
     <row r="63" spans="2:9">
@@ -6853,25 +6665,25 @@
         <v>59</v>
       </c>
       <c r="C63" s="15">
-        <v>969620</v>
+        <v>965919</v>
       </c>
       <c r="D63" s="12">
         <v>0.4407901692406536</v>
       </c>
       <c r="E63" s="16">
-        <v>2600115</v>
+        <v>2590192</v>
       </c>
       <c r="F63" s="15">
-        <v>1230111</v>
+        <v>1225416</v>
       </c>
       <c r="G63" s="12">
         <v>0.5592098307593465</v>
       </c>
       <c r="H63" s="16">
-        <v>3806128</v>
+        <v>3791602</v>
       </c>
       <c r="I63" s="15">
-        <v>2199731</v>
+        <v>2191335</v>
       </c>
     </row>
     <row r="64" spans="2:9">
@@ -6879,25 +6691,25 @@
         <v>60</v>
       </c>
       <c r="C64" s="18">
-        <v>1016633</v>
+        <v>1012606</v>
       </c>
       <c r="D64" s="19">
         <v>0.4391314954867041</v>
       </c>
       <c r="E64" s="20">
-        <v>2719275</v>
+        <v>2708503</v>
       </c>
       <c r="F64" s="18">
-        <v>1298466</v>
+        <v>1293323</v>
       </c>
       <c r="G64" s="19">
         <v>0.5608685045132958</v>
       </c>
       <c r="H64" s="20">
-        <v>4007444</v>
+        <v>3991570</v>
       </c>
       <c r="I64" s="18">
-        <v>2315100</v>
+        <v>2305929</v>
       </c>
     </row>
   </sheetData>
@@ -6924,7 +6736,7 @@
   <sheetData>
     <row r="2" spans="2:16">
       <c r="B2" s="1" t="s">
-        <v>157</v>
+        <v>141</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -6940,37 +6752,37 @@
     </row>
     <row r="4" spans="2:16">
       <c r="B4" s="21" t="s">
-        <v>158</v>
+        <v>142</v>
       </c>
       <c r="C4" s="21"/>
       <c r="D4" s="21" t="s">
-        <v>159</v>
+        <v>143</v>
       </c>
       <c r="E4" s="21"/>
       <c r="F4" s="21" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
       <c r="G4" s="21"/>
       <c r="H4" s="21" t="s">
-        <v>161</v>
+        <v>145</v>
       </c>
       <c r="I4" s="21"/>
       <c r="J4" s="21" t="s">
-        <v>162</v>
+        <v>146</v>
       </c>
       <c r="K4" s="21"/>
     </row>
     <row r="5" spans="2:16">
       <c r="B5" s="22">
-        <v>39525368</v>
+        <v>39715677</v>
       </c>
       <c r="C5" s="22"/>
       <c r="D5" s="22">
-        <v>530149339</v>
+        <v>527969495</v>
       </c>
       <c r="E5" s="22"/>
       <c r="F5" s="22">
-        <v>447031419</v>
+        <v>445113156</v>
       </c>
       <c r="G5" s="22"/>
       <c r="H5" s="23">
@@ -6978,55 +6790,55 @@
       </c>
       <c r="I5" s="23"/>
       <c r="J5" s="24" t="s">
-        <v>163</v>
+        <v>147</v>
       </c>
       <c r="K5" s="24"/>
     </row>
     <row r="8" spans="2:16" ht="35" customHeight="1">
       <c r="B8" s="25" t="s">
+        <v>133</v>
+      </c>
+      <c r="C8" s="25" t="s">
+        <v>148</v>
+      </c>
+      <c r="D8" s="25" t="s">
         <v>149</v>
       </c>
-      <c r="C8" s="25" t="s">
-        <v>164</v>
-      </c>
-      <c r="D8" s="25" t="s">
-        <v>165</v>
-      </c>
       <c r="E8" s="25" t="s">
-        <v>166</v>
+        <v>150</v>
       </c>
       <c r="F8" s="25" t="s">
-        <v>167</v>
+        <v>151</v>
       </c>
       <c r="G8" s="25" t="s">
-        <v>168</v>
+        <v>152</v>
       </c>
       <c r="H8" s="25" t="s">
-        <v>169</v>
+        <v>153</v>
       </c>
       <c r="I8" s="25" t="s">
-        <v>170</v>
+        <v>154</v>
       </c>
       <c r="J8" s="25" t="s">
-        <v>171</v>
+        <v>155</v>
       </c>
       <c r="K8" s="25" t="s">
-        <v>172</v>
+        <v>156</v>
       </c>
       <c r="L8" s="25" t="s">
-        <v>173</v>
+        <v>157</v>
       </c>
       <c r="M8" s="25" t="s">
-        <v>174</v>
+        <v>158</v>
       </c>
       <c r="N8" s="25" t="s">
-        <v>175</v>
+        <v>159</v>
       </c>
       <c r="O8" s="25" t="s">
-        <v>176</v>
+        <v>160</v>
       </c>
       <c r="P8" s="25" t="s">
-        <v>177</v>
+        <v>161</v>
       </c>
     </row>
     <row r="9" spans="2:16">
@@ -7034,46 +6846,46 @@
         <v>1</v>
       </c>
       <c r="C9" s="15">
-        <v>867839</v>
+        <v>776210</v>
       </c>
       <c r="D9" s="16">
-        <v>2142695</v>
+        <v>1916462</v>
       </c>
       <c r="E9" s="15">
-        <v>165731</v>
+        <v>165734</v>
       </c>
       <c r="F9" s="13">
         <v>5.97</v>
       </c>
       <c r="G9" s="16">
-        <v>1185616</v>
+        <v>1186295</v>
       </c>
       <c r="H9" s="16">
-        <v>660396</v>
+        <v>660775</v>
       </c>
       <c r="I9" s="15">
-        <v>40880</v>
+        <v>41019</v>
       </c>
       <c r="J9" s="15">
-        <v>124851</v>
+        <v>124715</v>
       </c>
       <c r="K9" s="12">
-        <v>0.2466666666666667</v>
+        <v>0.2475</v>
       </c>
       <c r="L9" s="26">
         <v>0.9</v>
       </c>
       <c r="M9" s="16">
-        <v>2803092</v>
+        <v>2577237</v>
       </c>
       <c r="N9" s="16">
-        <v>1966721</v>
+        <v>1767969</v>
       </c>
       <c r="O9" s="16">
-        <v>2803092</v>
+        <v>2577237</v>
       </c>
       <c r="P9" s="16">
-        <v>1966721</v>
+        <v>1767969</v>
       </c>
     </row>
     <row r="10" spans="2:16">
@@ -7081,46 +6893,46 @@
         <v>2</v>
       </c>
       <c r="C10" s="18">
-        <v>867679</v>
+        <v>900221</v>
       </c>
       <c r="D10" s="20">
-        <v>2142300</v>
+        <v>2222646</v>
       </c>
       <c r="E10" s="18">
-        <v>260230</v>
+        <v>260238</v>
       </c>
       <c r="F10" s="20">
         <v>5.96</v>
       </c>
       <c r="G10" s="20">
-        <v>1852792</v>
+        <v>1854916</v>
       </c>
       <c r="H10" s="20">
-        <v>1032266</v>
+        <v>1033450</v>
       </c>
       <c r="I10" s="18">
-        <v>63323</v>
+        <v>63758</v>
       </c>
       <c r="J10" s="18">
-        <v>196907</v>
+        <v>196480</v>
       </c>
       <c r="K10" s="19">
-        <v>0.2433333333333333</v>
+        <v>0.245</v>
       </c>
       <c r="L10" s="17">
         <v>1.05</v>
       </c>
       <c r="M10" s="20">
-        <v>3174566</v>
+        <v>3256096</v>
       </c>
       <c r="N10" s="20">
-        <v>2293618</v>
+        <v>2365365</v>
       </c>
       <c r="O10" s="20">
-        <v>5977658</v>
+        <v>5833334</v>
       </c>
       <c r="P10" s="20">
-        <v>4260339</v>
+        <v>4133334</v>
       </c>
     </row>
     <row r="11" spans="2:16">
@@ -7128,46 +6940,46 @@
         <v>3</v>
       </c>
       <c r="C11" s="15">
-        <v>867519</v>
+        <v>852659</v>
       </c>
       <c r="D11" s="16">
-        <v>2141905</v>
+        <v>2105215</v>
       </c>
       <c r="E11" s="15">
-        <v>331086</v>
+        <v>331100</v>
       </c>
       <c r="F11" s="13">
         <v>5.94</v>
       </c>
       <c r="G11" s="16">
-        <v>2346045</v>
+        <v>2350082</v>
       </c>
       <c r="H11" s="16">
-        <v>1307392</v>
+        <v>1309641</v>
       </c>
       <c r="I11" s="15">
-        <v>79461</v>
+        <v>80292</v>
       </c>
       <c r="J11" s="15">
-        <v>251625</v>
+        <v>250808</v>
       </c>
       <c r="K11" s="12">
-        <v>0.24</v>
+        <v>0.2425</v>
       </c>
       <c r="L11" s="26">
         <v>1</v>
       </c>
       <c r="M11" s="16">
-        <v>3449297</v>
+        <v>3414857</v>
       </c>
       <c r="N11" s="16">
-        <v>2535381</v>
+        <v>2505074</v>
       </c>
       <c r="O11" s="16">
-        <v>9426954</v>
+        <v>9248190</v>
       </c>
       <c r="P11" s="16">
-        <v>6795720</v>
+        <v>6638408</v>
       </c>
     </row>
     <row r="12" spans="2:16">
@@ -7175,46 +6987,46 @@
         <v>4</v>
       </c>
       <c r="C12" s="18">
-        <v>867360</v>
+        <v>848340</v>
       </c>
       <c r="D12" s="20">
-        <v>2141511</v>
+        <v>2094550</v>
       </c>
       <c r="E12" s="18">
-        <v>435633</v>
+        <v>435655</v>
       </c>
       <c r="F12" s="20">
         <v>5.93</v>
       </c>
       <c r="G12" s="20">
-        <v>3072145</v>
+        <v>3079186</v>
       </c>
       <c r="H12" s="20">
-        <v>1712440</v>
+        <v>1716365</v>
       </c>
       <c r="I12" s="18">
-        <v>103100</v>
+        <v>104557</v>
       </c>
       <c r="J12" s="18">
-        <v>332533</v>
+        <v>331098</v>
       </c>
       <c r="K12" s="19">
-        <v>0.2366666666666667</v>
+        <v>0.24</v>
       </c>
       <c r="L12" s="17">
         <v>1</v>
       </c>
       <c r="M12" s="20">
-        <v>3853951</v>
+        <v>3810915</v>
       </c>
       <c r="N12" s="20">
-        <v>2891477</v>
+        <v>2853605</v>
       </c>
       <c r="O12" s="20">
-        <v>13280906</v>
+        <v>13059106</v>
       </c>
       <c r="P12" s="20">
-        <v>9687197</v>
+        <v>9492013</v>
       </c>
     </row>
     <row r="13" spans="2:16">
@@ -7222,46 +7034,46 @@
         <v>5</v>
       </c>
       <c r="C13" s="15">
-        <v>867200</v>
+        <v>886583</v>
       </c>
       <c r="D13" s="16">
-        <v>2141118</v>
+        <v>2188974</v>
       </c>
       <c r="E13" s="15">
-        <v>590821</v>
+        <v>590853</v>
       </c>
       <c r="F13" s="13">
         <v>5.91</v>
       </c>
       <c r="G13" s="16">
-        <v>4146672</v>
+        <v>4158548</v>
       </c>
       <c r="H13" s="16">
-        <v>2311945</v>
+        <v>2318566</v>
       </c>
       <c r="I13" s="15">
-        <v>137858</v>
+        <v>140328</v>
       </c>
       <c r="J13" s="15">
-        <v>452963</v>
+        <v>450525</v>
       </c>
       <c r="K13" s="12">
-        <v>0.2333333333333333</v>
+        <v>0.2375</v>
       </c>
       <c r="L13" s="26">
         <v>1.05</v>
       </c>
       <c r="M13" s="16">
-        <v>4453063</v>
+        <v>4507540</v>
       </c>
       <c r="N13" s="16">
-        <v>3418695</v>
+        <v>3466635</v>
       </c>
       <c r="O13" s="16">
-        <v>17733969</v>
+        <v>17566646</v>
       </c>
       <c r="P13" s="16">
-        <v>13105892</v>
+        <v>12958648</v>
       </c>
     </row>
     <row r="14" spans="2:16">
@@ -7269,46 +7081,46 @@
         <v>6</v>
       </c>
       <c r="C14" s="18">
-        <v>867042</v>
+        <v>924778</v>
       </c>
       <c r="D14" s="20">
-        <v>2140726</v>
+        <v>2283277</v>
       </c>
       <c r="E14" s="18">
-        <v>782743</v>
+        <v>782786</v>
       </c>
       <c r="F14" s="20">
         <v>5.9</v>
       </c>
       <c r="G14" s="20">
-        <v>5467432</v>
+        <v>5486210</v>
       </c>
       <c r="H14" s="20">
-        <v>3049056</v>
+        <v>3059528</v>
       </c>
       <c r="I14" s="18">
-        <v>180031</v>
+        <v>183955</v>
       </c>
       <c r="J14" s="18">
-        <v>602712</v>
+        <v>598831</v>
       </c>
       <c r="K14" s="19">
-        <v>0.23</v>
+        <v>0.235</v>
       </c>
       <c r="L14" s="17">
         <v>1.1</v>
       </c>
       <c r="M14" s="20">
-        <v>5189782</v>
+        <v>5342806</v>
       </c>
       <c r="N14" s="20">
-        <v>4067008</v>
+        <v>4201669</v>
       </c>
       <c r="O14" s="20">
-        <v>22923751</v>
+        <v>22909451</v>
       </c>
       <c r="P14" s="20">
-        <v>17172901</v>
+        <v>17160317</v>
       </c>
     </row>
     <row r="15" spans="2:16">
@@ -7316,46 +7128,46 @@
         <v>7</v>
       </c>
       <c r="C15" s="15">
-        <v>866883</v>
+        <v>879209</v>
       </c>
       <c r="D15" s="16">
-        <v>2140335</v>
+        <v>2170768</v>
       </c>
       <c r="E15" s="15">
-        <v>923335</v>
+        <v>923385</v>
       </c>
       <c r="F15" s="13">
         <v>5.88</v>
       </c>
       <c r="G15" s="16">
-        <v>6418626</v>
+        <v>6444331</v>
       </c>
       <c r="H15" s="16">
-        <v>3580372</v>
+        <v>3594711</v>
       </c>
       <c r="I15" s="15">
-        <v>209289</v>
+        <v>214687</v>
       </c>
       <c r="J15" s="15">
-        <v>714046</v>
+        <v>708698</v>
       </c>
       <c r="K15" s="12">
-        <v>0.2266666666666667</v>
+        <v>0.2325</v>
       </c>
       <c r="L15" s="26">
         <v>1.05</v>
       </c>
       <c r="M15" s="16">
-        <v>5720707</v>
+        <v>5765479</v>
       </c>
       <c r="N15" s="16">
-        <v>4534222</v>
+        <v>4573621</v>
       </c>
       <c r="O15" s="16">
-        <v>28644458</v>
+        <v>28674930</v>
       </c>
       <c r="P15" s="16">
-        <v>21707123</v>
+        <v>21733938</v>
       </c>
     </row>
     <row r="16" spans="2:16">
@@ -7363,46 +7175,46 @@
         <v>8</v>
       </c>
       <c r="C16" s="18">
-        <v>866725</v>
+        <v>834246</v>
       </c>
       <c r="D16" s="20">
-        <v>2139944</v>
+        <v>2059752</v>
       </c>
       <c r="E16" s="18">
-        <v>1058318</v>
+        <v>1058370</v>
       </c>
       <c r="F16" s="20">
         <v>5.87</v>
       </c>
       <c r="G16" s="20">
-        <v>7321753</v>
+        <v>7355245</v>
       </c>
       <c r="H16" s="20">
-        <v>4085125</v>
+        <v>4103812</v>
       </c>
       <c r="I16" s="18">
-        <v>236358</v>
+        <v>243425</v>
       </c>
       <c r="J16" s="18">
-        <v>821960</v>
+        <v>814945</v>
       </c>
       <c r="K16" s="19">
-        <v>0.2233333333333333</v>
+        <v>0.23</v>
       </c>
       <c r="L16" s="17">
         <v>1</v>
       </c>
       <c r="M16" s="20">
-        <v>6225069</v>
+        <v>6163564</v>
       </c>
       <c r="N16" s="20">
-        <v>4978061</v>
+        <v>4923936</v>
       </c>
       <c r="O16" s="20">
-        <v>34869527</v>
+        <v>34838494</v>
       </c>
       <c r="P16" s="20">
-        <v>26685184</v>
+        <v>26657875</v>
       </c>
     </row>
     <row r="17" spans="2:16">
@@ -7410,46 +7222,46 @@
         <v>9</v>
       </c>
       <c r="C17" s="15">
-        <v>866567</v>
+        <v>789826</v>
       </c>
       <c r="D17" s="16">
-        <v>2139555</v>
+        <v>1950081</v>
       </c>
       <c r="E17" s="15">
-        <v>1177385</v>
+        <v>1177434</v>
       </c>
       <c r="F17" s="13">
         <v>5.85</v>
       </c>
       <c r="G17" s="16">
-        <v>8106462</v>
+        <v>8148160</v>
       </c>
       <c r="H17" s="16">
-        <v>4524032</v>
+        <v>4547302</v>
       </c>
       <c r="I17" s="15">
-        <v>259025</v>
+        <v>267866</v>
       </c>
       <c r="J17" s="15">
-        <v>918360</v>
+        <v>909568</v>
       </c>
       <c r="K17" s="12">
-        <v>0.22</v>
+        <v>0.2275</v>
       </c>
       <c r="L17" s="26">
         <v>0.95</v>
       </c>
       <c r="M17" s="16">
-        <v>6663587</v>
+        <v>6497384</v>
       </c>
       <c r="N17" s="16">
-        <v>5363957</v>
+        <v>5217698</v>
       </c>
       <c r="O17" s="16">
-        <v>41533114</v>
+        <v>41335878</v>
       </c>
       <c r="P17" s="16">
-        <v>32049140</v>
+        <v>31875572</v>
       </c>
     </row>
     <row r="18" spans="2:16">
@@ -7457,46 +7269,46 @@
         <v>10</v>
       </c>
       <c r="C18" s="18">
-        <v>866410</v>
+        <v>787336</v>
       </c>
       <c r="D18" s="20">
-        <v>2139167</v>
+        <v>1943932</v>
       </c>
       <c r="E18" s="18">
-        <v>1341260</v>
+        <v>1341301</v>
       </c>
       <c r="F18" s="20">
         <v>5.84</v>
       </c>
       <c r="G18" s="20">
-        <v>9190470</v>
+        <v>9242973</v>
       </c>
       <c r="H18" s="20">
-        <v>5130220</v>
+        <v>5159528</v>
       </c>
       <c r="I18" s="18">
-        <v>290606</v>
+        <v>301793</v>
       </c>
       <c r="J18" s="18">
-        <v>1050654</v>
+        <v>1039508</v>
       </c>
       <c r="K18" s="19">
-        <v>0.2166666666666667</v>
+        <v>0.225</v>
       </c>
       <c r="L18" s="17">
         <v>0.95</v>
       </c>
       <c r="M18" s="20">
-        <v>7269387</v>
+        <v>7103460</v>
       </c>
       <c r="N18" s="20">
-        <v>5897061</v>
+        <v>5751045</v>
       </c>
       <c r="O18" s="20">
-        <v>48802501</v>
+        <v>48439338</v>
       </c>
       <c r="P18" s="20">
-        <v>37946201</v>
+        <v>37626617</v>
       </c>
     </row>
     <row r="19" spans="2:16">
@@ -7504,46 +7316,46 @@
         <v>11</v>
       </c>
       <c r="C19" s="15">
-        <v>866253</v>
+        <v>785044</v>
       </c>
       <c r="D19" s="16">
-        <v>2138779</v>
+        <v>1938273</v>
       </c>
       <c r="E19" s="15">
-        <v>1490378</v>
+        <v>1490403</v>
       </c>
       <c r="F19" s="13">
         <v>5.83</v>
       </c>
       <c r="G19" s="16">
-        <v>10163204</v>
+        <v>10227043</v>
       </c>
       <c r="H19" s="16">
-        <v>5674570</v>
+        <v>5710214</v>
       </c>
       <c r="I19" s="15">
-        <v>317947</v>
+        <v>331615</v>
       </c>
       <c r="J19" s="15">
-        <v>1172431</v>
+        <v>1158788</v>
       </c>
       <c r="K19" s="12">
-        <v>0.2133333333333333</v>
+        <v>0.2225</v>
       </c>
       <c r="L19" s="26">
         <v>0.95</v>
       </c>
       <c r="M19" s="16">
-        <v>7813349</v>
+        <v>7648487</v>
       </c>
       <c r="N19" s="16">
-        <v>6375747</v>
+        <v>6230668</v>
       </c>
       <c r="O19" s="16">
-        <v>56615850</v>
+        <v>56087824</v>
       </c>
       <c r="P19" s="16">
-        <v>44321948</v>
+        <v>43857285</v>
       </c>
     </row>
     <row r="20" spans="2:16">
@@ -7551,10 +7363,10 @@
         <v>12</v>
       </c>
       <c r="C20" s="18">
-        <v>866097</v>
+        <v>824142</v>
       </c>
       <c r="D20" s="20">
-        <v>2138392</v>
+        <v>2034806</v>
       </c>
       <c r="E20" s="18">
         <v>1703807</v>
@@ -7563,34 +7375,34 @@
         <v>5.81</v>
       </c>
       <c r="G20" s="20">
-        <v>11562769</v>
+        <v>11641968</v>
       </c>
       <c r="H20" s="20">
-        <v>6457554</v>
+        <v>6501785</v>
       </c>
       <c r="I20" s="18">
-        <v>357799</v>
+        <v>374838</v>
       </c>
       <c r="J20" s="18">
-        <v>1346008</v>
+        <v>1328969</v>
       </c>
       <c r="K20" s="19">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="L20" s="17">
         <v>1</v>
       </c>
       <c r="M20" s="20">
-        <v>8595947</v>
+        <v>8536592</v>
       </c>
       <c r="N20" s="20">
-        <v>7064433</v>
+        <v>7012201</v>
       </c>
       <c r="O20" s="20">
-        <v>65211797</v>
+        <v>64624416</v>
       </c>
       <c r="P20" s="20">
-        <v>51386381</v>
+        <v>50869486</v>
       </c>
     </row>
     <row r="21" spans="2:16">
@@ -7598,46 +7410,46 @@
         <v>13</v>
       </c>
       <c r="C21" s="15">
-        <v>865940</v>
+        <v>739889</v>
       </c>
       <c r="D21" s="16">
-        <v>2138007</v>
+        <v>1826787</v>
       </c>
       <c r="E21" s="15">
-        <v>1639299</v>
+        <v>1639267</v>
       </c>
       <c r="F21" s="13">
         <v>5.8</v>
       </c>
       <c r="G21" s="16">
-        <v>11071451</v>
+        <v>11153572</v>
       </c>
       <c r="H21" s="16">
-        <v>6184643</v>
+        <v>6230517</v>
       </c>
       <c r="I21" s="15">
-        <v>338788</v>
+        <v>356541</v>
       </c>
       <c r="J21" s="15">
-        <v>1300511</v>
+        <v>1282726</v>
       </c>
       <c r="K21" s="12">
-        <v>0.2066666666666667</v>
+        <v>0.2175</v>
       </c>
       <c r="L21" s="26">
         <v>0.9</v>
       </c>
       <c r="M21" s="16">
-        <v>8322650</v>
+        <v>8057304</v>
       </c>
       <c r="N21" s="16">
-        <v>6823932</v>
+        <v>6590427</v>
       </c>
       <c r="O21" s="16">
-        <v>73534446</v>
+        <v>72681719</v>
       </c>
       <c r="P21" s="16">
-        <v>58210313</v>
+        <v>57459913</v>
       </c>
     </row>
     <row r="22" spans="2:16">
@@ -7645,46 +7457,46 @@
         <v>14</v>
       </c>
       <c r="C22" s="18">
-        <v>865784</v>
+        <v>861231</v>
       </c>
       <c r="D22" s="20">
-        <v>2137622</v>
+        <v>2126379</v>
       </c>
       <c r="E22" s="18">
-        <v>2004047</v>
+        <v>2003961</v>
       </c>
       <c r="F22" s="20">
         <v>5.78</v>
       </c>
       <c r="G22" s="20">
-        <v>13469669</v>
+        <v>13577220</v>
       </c>
       <c r="H22" s="20">
-        <v>7526115</v>
+        <v>7586209</v>
       </c>
       <c r="I22" s="18">
-        <v>407490</v>
+        <v>430852</v>
       </c>
       <c r="J22" s="18">
-        <v>1596557</v>
+        <v>1573109</v>
       </c>
       <c r="K22" s="19">
-        <v>0.2033333333333333</v>
+        <v>0.215</v>
       </c>
       <c r="L22" s="17">
         <v>1.05</v>
       </c>
       <c r="M22" s="20">
-        <v>9663737</v>
+        <v>9712588</v>
       </c>
       <c r="N22" s="20">
-        <v>8004089</v>
+        <v>8047077</v>
       </c>
       <c r="O22" s="20">
-        <v>83198183</v>
+        <v>82394307</v>
       </c>
       <c r="P22" s="20">
-        <v>66214401</v>
+        <v>65506990</v>
       </c>
     </row>
     <row r="23" spans="2:16">
@@ -7692,46 +7504,46 @@
         <v>15</v>
       </c>
       <c r="C23" s="15">
-        <v>865629</v>
+        <v>818490</v>
       </c>
       <c r="D23" s="16">
-        <v>2137238</v>
+        <v>2020853</v>
       </c>
       <c r="E23" s="15">
-        <v>1983550</v>
+        <v>1983414</v>
       </c>
       <c r="F23" s="13">
         <v>5.77</v>
       </c>
       <c r="G23" s="16">
-        <v>13267605</v>
+        <v>13381066</v>
       </c>
       <c r="H23" s="16">
-        <v>7414985</v>
+        <v>7478396</v>
       </c>
       <c r="I23" s="15">
-        <v>396710</v>
+        <v>421475</v>
       </c>
       <c r="J23" s="15">
-        <v>1586840</v>
+        <v>1561939</v>
       </c>
       <c r="K23" s="12">
-        <v>0.2</v>
+        <v>0.2125</v>
       </c>
       <c r="L23" s="26">
         <v>1</v>
       </c>
       <c r="M23" s="16">
-        <v>9552223</v>
+        <v>9499249</v>
       </c>
       <c r="N23" s="16">
-        <v>7905956</v>
+        <v>7859339</v>
       </c>
       <c r="O23" s="16">
-        <v>92750407</v>
+        <v>91893556</v>
       </c>
       <c r="P23" s="16">
-        <v>74120358</v>
+        <v>73366329</v>
       </c>
     </row>
     <row r="24" spans="2:16">
@@ -7739,46 +7551,46 @@
         <v>16</v>
       </c>
       <c r="C24" s="18">
-        <v>865474</v>
+        <v>816899</v>
       </c>
       <c r="D24" s="20">
-        <v>2136855</v>
+        <v>2016923</v>
       </c>
       <c r="E24" s="18">
-        <v>2040544</v>
+        <v>2040347</v>
       </c>
       <c r="F24" s="20">
         <v>5.75</v>
       </c>
       <c r="G24" s="20">
-        <v>13582934</v>
+        <v>13706798</v>
       </c>
       <c r="H24" s="20">
-        <v>7593030</v>
+        <v>7662272</v>
       </c>
       <c r="I24" s="18">
-        <v>401307</v>
+        <v>428473</v>
       </c>
       <c r="J24" s="18">
-        <v>1639237</v>
+        <v>1611874</v>
       </c>
       <c r="K24" s="19">
-        <v>0.1966666666666667</v>
+        <v>0.21</v>
       </c>
       <c r="L24" s="17">
         <v>1</v>
       </c>
       <c r="M24" s="20">
-        <v>9729885</v>
+        <v>9679195</v>
       </c>
       <c r="N24" s="20">
-        <v>8062299</v>
+        <v>8017692</v>
       </c>
       <c r="O24" s="20">
-        <v>102480292</v>
+        <v>101572751</v>
       </c>
       <c r="P24" s="20">
-        <v>82182657</v>
+        <v>81384021</v>
       </c>
     </row>
     <row r="25" spans="2:16">
@@ -7786,46 +7598,46 @@
         <v>17</v>
       </c>
       <c r="C25" s="15">
-        <v>865319</v>
+        <v>856206</v>
       </c>
       <c r="D25" s="16">
-        <v>2136472</v>
+        <v>2113974</v>
       </c>
       <c r="E25" s="15">
-        <v>2186390</v>
+        <v>2186110</v>
       </c>
       <c r="F25" s="13">
         <v>5.74</v>
       </c>
       <c r="G25" s="16">
-        <v>14483416</v>
+        <v>14623701</v>
       </c>
       <c r="H25" s="16">
-        <v>8098345</v>
+        <v>8176785</v>
       </c>
       <c r="I25" s="15">
-        <v>422702</v>
+        <v>453618</v>
       </c>
       <c r="J25" s="15">
-        <v>1763688</v>
+        <v>1732492</v>
       </c>
       <c r="K25" s="12">
-        <v>0.1933333333333333</v>
+        <v>0.2075</v>
       </c>
       <c r="L25" s="26">
         <v>1.05</v>
       </c>
       <c r="M25" s="16">
-        <v>10234817</v>
+        <v>10290758</v>
       </c>
       <c r="N25" s="16">
-        <v>8506639</v>
+        <v>8555867</v>
       </c>
       <c r="O25" s="16">
-        <v>112715109</v>
+        <v>111863509</v>
       </c>
       <c r="P25" s="16">
-        <v>90689296</v>
+        <v>89939888</v>
       </c>
     </row>
     <row r="26" spans="2:16">
@@ -7833,46 +7645,46 @@
         <v>18</v>
       </c>
       <c r="C26" s="18">
-        <v>865165</v>
+        <v>895496</v>
       </c>
       <c r="D26" s="20">
-        <v>2136091</v>
+        <v>2210980</v>
       </c>
       <c r="E26" s="18">
-        <v>2325049</v>
+        <v>2324671</v>
       </c>
       <c r="F26" s="20">
         <v>5.72</v>
       </c>
       <c r="G26" s="20">
-        <v>15327419</v>
+        <v>15484564</v>
       </c>
       <c r="H26" s="20">
-        <v>8572312</v>
+        <v>8660200</v>
       </c>
       <c r="I26" s="18">
-        <v>441759</v>
+        <v>476558</v>
       </c>
       <c r="J26" s="18">
-        <v>1883290</v>
+        <v>1848113</v>
       </c>
       <c r="K26" s="19">
-        <v>0.19</v>
+        <v>0.205</v>
       </c>
       <c r="L26" s="17">
         <v>1.1</v>
       </c>
       <c r="M26" s="20">
-        <v>10708403</v>
+        <v>10871180</v>
       </c>
       <c r="N26" s="20">
-        <v>8923395</v>
+        <v>9066638</v>
       </c>
       <c r="O26" s="20">
-        <v>123423512</v>
+        <v>122734689</v>
       </c>
       <c r="P26" s="20">
-        <v>99612691</v>
+        <v>99006526</v>
       </c>
     </row>
     <row r="27" spans="2:16">
@@ -7880,46 +7692,46 @@
         <v>19</v>
       </c>
       <c r="C27" s="15">
-        <v>865010</v>
+        <v>853490</v>
       </c>
       <c r="D27" s="16">
-        <v>2135711</v>
+        <v>2107266</v>
       </c>
       <c r="E27" s="15">
-        <v>2248320</v>
+        <v>2247871</v>
       </c>
       <c r="F27" s="13">
         <v>5.71</v>
       </c>
       <c r="G27" s="16">
-        <v>14749800</v>
+        <v>14909382</v>
       </c>
       <c r="H27" s="16">
-        <v>8251231</v>
+        <v>8340503</v>
       </c>
       <c r="I27" s="15">
-        <v>419686</v>
+        <v>455194</v>
       </c>
       <c r="J27" s="15">
-        <v>1828634</v>
+        <v>1792677</v>
       </c>
       <c r="K27" s="12">
-        <v>0.1866666666666667</v>
+        <v>0.2025</v>
       </c>
       <c r="L27" s="26">
         <v>1.05</v>
       </c>
       <c r="M27" s="16">
-        <v>10386941</v>
+        <v>10447770</v>
       </c>
       <c r="N27" s="16">
-        <v>8890509</v>
+        <v>8944037</v>
       </c>
       <c r="O27" s="16">
-        <v>133810454</v>
+        <v>133182459</v>
       </c>
       <c r="P27" s="16">
-        <v>108503199</v>
+        <v>107950564</v>
       </c>
     </row>
     <row r="28" spans="2:16">
@@ -7927,46 +7739,46 @@
         <v>20</v>
       </c>
       <c r="C28" s="18">
-        <v>864857</v>
+        <v>811707</v>
       </c>
       <c r="D28" s="20">
-        <v>2135331</v>
+        <v>2004104</v>
       </c>
       <c r="E28" s="18">
-        <v>2163231</v>
+        <v>2162714</v>
       </c>
       <c r="F28" s="20">
         <v>5.69</v>
       </c>
       <c r="G28" s="20">
-        <v>14122766</v>
+        <v>14283570</v>
       </c>
       <c r="H28" s="20">
-        <v>7902344</v>
+        <v>7992322</v>
       </c>
       <c r="I28" s="18">
-        <v>396592</v>
+        <v>432543</v>
       </c>
       <c r="J28" s="18">
-        <v>1766639</v>
+        <v>1730171</v>
       </c>
       <c r="K28" s="19">
-        <v>0.1833333333333333</v>
+        <v>0.2</v>
       </c>
       <c r="L28" s="17">
         <v>1</v>
       </c>
       <c r="M28" s="20">
-        <v>10037676</v>
+        <v>9996426</v>
       </c>
       <c r="N28" s="20">
-        <v>8583155</v>
+        <v>8546855</v>
       </c>
       <c r="O28" s="20">
-        <v>143848129</v>
+        <v>143178885</v>
       </c>
       <c r="P28" s="20">
-        <v>117086354</v>
+        <v>116497418</v>
       </c>
     </row>
     <row r="29" spans="2:16">
@@ -7974,46 +7786,46 @@
         <v>21</v>
       </c>
       <c r="C29" s="15">
-        <v>864703</v>
+        <v>770124</v>
       </c>
       <c r="D29" s="16">
-        <v>2134952</v>
+        <v>1901436</v>
       </c>
       <c r="E29" s="15">
-        <v>2072069</v>
+        <v>2071486</v>
       </c>
       <c r="F29" s="13">
         <v>5.68</v>
       </c>
       <c r="G29" s="16">
-        <v>13461936</v>
+        <v>13622846</v>
       </c>
       <c r="H29" s="16">
-        <v>7534376</v>
+        <v>7624434</v>
       </c>
       <c r="I29" s="15">
-        <v>372972</v>
+        <v>409118</v>
       </c>
       <c r="J29" s="15">
-        <v>1699097</v>
+        <v>1662368</v>
       </c>
       <c r="K29" s="12">
-        <v>0.18</v>
+        <v>0.1975</v>
       </c>
       <c r="L29" s="26">
         <v>0.95</v>
       </c>
       <c r="M29" s="16">
-        <v>9669329</v>
+        <v>9525870</v>
       </c>
       <c r="N29" s="16">
-        <v>8259009</v>
+        <v>8132766</v>
       </c>
       <c r="O29" s="16">
-        <v>153517458</v>
+        <v>152704755</v>
       </c>
       <c r="P29" s="16">
-        <v>125345363</v>
+        <v>124630184</v>
       </c>
     </row>
     <row r="30" spans="2:16">
@@ -8021,46 +7833,46 @@
         <v>22</v>
       </c>
       <c r="C30" s="18">
-        <v>864550</v>
+        <v>769206</v>
       </c>
       <c r="D30" s="20">
-        <v>2134575</v>
+        <v>1899171</v>
       </c>
       <c r="E30" s="18">
-        <v>2083356</v>
+        <v>2082675</v>
       </c>
       <c r="F30" s="20">
         <v>5.66</v>
       </c>
       <c r="G30" s="20">
-        <v>13469483</v>
+        <v>13638118</v>
       </c>
       <c r="H30" s="20">
-        <v>7540397</v>
+        <v>7634801</v>
       </c>
       <c r="I30" s="18">
-        <v>368060</v>
+        <v>406122</v>
       </c>
       <c r="J30" s="18">
-        <v>1715296</v>
+        <v>1676553</v>
       </c>
       <c r="K30" s="19">
-        <v>0.1766666666666667</v>
+        <v>0.195</v>
       </c>
       <c r="L30" s="17">
         <v>0.95</v>
       </c>
       <c r="M30" s="20">
-        <v>9674972</v>
+        <v>9533972</v>
       </c>
       <c r="N30" s="20">
-        <v>8263975</v>
+        <v>8139896</v>
       </c>
       <c r="O30" s="20">
-        <v>163192430</v>
+        <v>162238727</v>
       </c>
       <c r="P30" s="20">
-        <v>133609338</v>
+        <v>132770080</v>
       </c>
     </row>
     <row r="31" spans="2:16">
@@ -8068,46 +7880,46 @@
         <v>23</v>
       </c>
       <c r="C31" s="15">
-        <v>864398</v>
+        <v>768362</v>
       </c>
       <c r="D31" s="16">
-        <v>2134198</v>
+        <v>1897086</v>
       </c>
       <c r="E31" s="15">
-        <v>2092297</v>
+        <v>2091513</v>
       </c>
       <c r="F31" s="13">
         <v>5.65</v>
       </c>
       <c r="G31" s="16">
-        <v>13461472</v>
+        <v>13637632</v>
       </c>
       <c r="H31" s="16">
-        <v>7537709</v>
+        <v>7636349</v>
       </c>
       <c r="I31" s="15">
-        <v>362665</v>
+        <v>402616</v>
       </c>
       <c r="J31" s="15">
-        <v>1729632</v>
+        <v>1688897</v>
       </c>
       <c r="K31" s="12">
-        <v>0.1733333333333333</v>
+        <v>0.1925</v>
       </c>
       <c r="L31" s="26">
         <v>0.95</v>
       </c>
       <c r="M31" s="16">
-        <v>9671906</v>
+        <v>9533435</v>
       </c>
       <c r="N31" s="16">
-        <v>8261278</v>
+        <v>8139423</v>
       </c>
       <c r="O31" s="16">
-        <v>172864336</v>
+        <v>171772163</v>
       </c>
       <c r="P31" s="16">
-        <v>141870616</v>
+        <v>140909503</v>
       </c>
     </row>
     <row r="32" spans="2:16">
@@ -8115,46 +7927,46 @@
         <v>24</v>
       </c>
       <c r="C32" s="18">
-        <v>864245</v>
+        <v>807984</v>
       </c>
       <c r="D32" s="20">
-        <v>2133822</v>
+        <v>1994914</v>
       </c>
       <c r="E32" s="18">
-        <v>2207125</v>
+        <v>2206185</v>
       </c>
       <c r="F32" s="20">
         <v>5.64</v>
       </c>
       <c r="G32" s="20">
-        <v>14131087</v>
+        <v>14324011</v>
       </c>
       <c r="H32" s="20">
-        <v>7914542</v>
+        <v>8022595</v>
       </c>
       <c r="I32" s="18">
-        <v>375211</v>
+        <v>419175</v>
       </c>
       <c r="J32" s="18">
-        <v>1831914</v>
+        <v>1787010</v>
       </c>
       <c r="K32" s="19">
-        <v>0.17</v>
+        <v>0.19</v>
       </c>
       <c r="L32" s="17">
         <v>1</v>
       </c>
       <c r="M32" s="20">
-        <v>10048364</v>
+        <v>10017509</v>
       </c>
       <c r="N32" s="20">
-        <v>8592560</v>
+        <v>8565408</v>
       </c>
       <c r="O32" s="20">
-        <v>182912700</v>
+        <v>181789671</v>
       </c>
       <c r="P32" s="20">
-        <v>150463176</v>
+        <v>149474911</v>
       </c>
     </row>
     <row r="33" spans="2:16">
@@ -8162,46 +7974,46 @@
         <v>25</v>
       </c>
       <c r="C33" s="15">
-        <v>864093</v>
+        <v>726509</v>
       </c>
       <c r="D33" s="16">
-        <v>2133446</v>
+        <v>1793750</v>
       </c>
       <c r="E33" s="15">
-        <v>1997566</v>
+        <v>1996611</v>
       </c>
       <c r="F33" s="13">
         <v>5.62</v>
       </c>
       <c r="G33" s="16">
-        <v>12727022</v>
+        <v>12908009</v>
       </c>
       <c r="H33" s="16">
-        <v>7129851</v>
+        <v>7231242</v>
       </c>
       <c r="I33" s="15">
-        <v>332928</v>
+        <v>374365</v>
       </c>
       <c r="J33" s="15">
-        <v>1664638</v>
+        <v>1622246</v>
       </c>
       <c r="K33" s="12">
-        <v>0.1666666666666667</v>
+        <v>0.1875</v>
       </c>
       <c r="L33" s="26">
         <v>0.9</v>
       </c>
       <c r="M33" s="16">
-        <v>9263297</v>
+        <v>9024992</v>
       </c>
       <c r="N33" s="16">
-        <v>7901701</v>
+        <v>7691993</v>
       </c>
       <c r="O33" s="16">
-        <v>192175997</v>
+        <v>190814664</v>
       </c>
       <c r="P33" s="16">
-        <v>158364878</v>
+        <v>157166904</v>
       </c>
     </row>
     <row r="34" spans="2:16">
@@ -8209,46 +8021,46 @@
         <v>26</v>
       </c>
       <c r="C34" s="18">
-        <v>863942</v>
+        <v>846866</v>
       </c>
       <c r="D34" s="20">
-        <v>2133072</v>
+        <v>2090913</v>
       </c>
       <c r="E34" s="18">
-        <v>2326754</v>
+        <v>2325506</v>
       </c>
       <c r="F34" s="20">
         <v>5.61</v>
       </c>
       <c r="G34" s="20">
-        <v>14751994</v>
+        <v>14970108</v>
       </c>
       <c r="H34" s="20">
-        <v>8266235</v>
+        <v>8388455</v>
       </c>
       <c r="I34" s="18">
-        <v>380036</v>
+        <v>430219</v>
       </c>
       <c r="J34" s="18">
-        <v>1946718</v>
+        <v>1895287</v>
       </c>
       <c r="K34" s="19">
-        <v>0.1633333333333333</v>
+        <v>0.185</v>
       </c>
       <c r="L34" s="17">
         <v>1.05</v>
       </c>
       <c r="M34" s="20">
-        <v>10399307</v>
+        <v>10479368</v>
       </c>
       <c r="N34" s="20">
-        <v>8901390</v>
+        <v>8971844</v>
       </c>
       <c r="O34" s="20">
-        <v>202575304</v>
+        <v>201294031</v>
       </c>
       <c r="P34" s="20">
-        <v>167266268</v>
+        <v>166138748</v>
       </c>
     </row>
     <row r="35" spans="2:16">
@@ -8256,46 +8068,46 @@
         <v>27</v>
       </c>
       <c r="C35" s="15">
-        <v>863790</v>
+        <v>805902</v>
       </c>
       <c r="D35" s="16">
-        <v>2132699</v>
+        <v>1989773</v>
       </c>
       <c r="E35" s="15">
-        <v>2223172</v>
+        <v>2221849</v>
       </c>
       <c r="F35" s="13">
         <v>5.59</v>
       </c>
       <c r="G35" s="16">
-        <v>14026376</v>
+        <v>14241718</v>
       </c>
       <c r="H35" s="16">
-        <v>7861507</v>
+        <v>7982202</v>
       </c>
       <c r="I35" s="15">
-        <v>355708</v>
+        <v>405487</v>
       </c>
       <c r="J35" s="15">
-        <v>1867464</v>
+        <v>1816362</v>
       </c>
       <c r="K35" s="12">
-        <v>0.16</v>
+        <v>0.1825</v>
       </c>
       <c r="L35" s="26">
         <v>1</v>
       </c>
       <c r="M35" s="16">
-        <v>9994206</v>
+        <v>9971975</v>
       </c>
       <c r="N35" s="16">
-        <v>8544901</v>
+        <v>8525338</v>
       </c>
       <c r="O35" s="16">
-        <v>212569510</v>
+        <v>211266007</v>
       </c>
       <c r="P35" s="16">
-        <v>175811169</v>
+        <v>174664086</v>
       </c>
     </row>
     <row r="36" spans="2:16">
@@ -8303,46 +8115,46 @@
         <v>28</v>
       </c>
       <c r="C36" s="18">
-        <v>863640</v>
+        <v>805316</v>
       </c>
       <c r="D36" s="20">
-        <v>2132326</v>
+        <v>1988326</v>
       </c>
       <c r="E36" s="18">
-        <v>2227208</v>
+        <v>2225745</v>
       </c>
       <c r="F36" s="20">
         <v>5.58</v>
       </c>
       <c r="G36" s="20">
-        <v>13983079</v>
+        <v>14205687</v>
       </c>
       <c r="H36" s="20">
-        <v>7839105</v>
+        <v>7963902</v>
       </c>
       <c r="I36" s="18">
-        <v>348929</v>
+        <v>400634</v>
       </c>
       <c r="J36" s="18">
-        <v>1878279</v>
+        <v>1825111</v>
       </c>
       <c r="K36" s="19">
-        <v>0.1566666666666667</v>
+        <v>0.18</v>
       </c>
       <c r="L36" s="17">
         <v>1</v>
       </c>
       <c r="M36" s="20">
-        <v>9971431</v>
+        <v>9952227</v>
       </c>
       <c r="N36" s="20">
-        <v>8524859</v>
+        <v>8507960</v>
       </c>
       <c r="O36" s="20">
-        <v>222540941</v>
+        <v>221218234</v>
       </c>
       <c r="P36" s="20">
-        <v>184336028</v>
+        <v>183172046</v>
       </c>
     </row>
     <row r="37" spans="2:16">
@@ -8350,46 +8162,46 @@
         <v>29</v>
       </c>
       <c r="C37" s="15">
-        <v>863489</v>
+        <v>845016</v>
       </c>
       <c r="D37" s="16">
-        <v>2131954</v>
+        <v>2086343</v>
       </c>
       <c r="E37" s="15">
-        <v>2339569</v>
+        <v>2337879</v>
       </c>
       <c r="F37" s="13">
         <v>5.56</v>
       </c>
       <c r="G37" s="16">
-        <v>14616561</v>
+        <v>14857534</v>
       </c>
       <c r="H37" s="16">
-        <v>8196191</v>
+        <v>8331316</v>
       </c>
       <c r="I37" s="15">
-        <v>358734</v>
+        <v>414974</v>
       </c>
       <c r="J37" s="15">
-        <v>1980835</v>
+        <v>1922905</v>
       </c>
       <c r="K37" s="12">
-        <v>0.1533333333333333</v>
+        <v>0.1775</v>
       </c>
       <c r="L37" s="26">
         <v>1.05</v>
       </c>
       <c r="M37" s="16">
-        <v>10328146</v>
+        <v>10417660</v>
       </c>
       <c r="N37" s="16">
-        <v>8838768</v>
+        <v>8917541</v>
       </c>
       <c r="O37" s="16">
-        <v>232869087</v>
+        <v>231635894</v>
       </c>
       <c r="P37" s="16">
-        <v>193174796</v>
+        <v>192089586</v>
       </c>
     </row>
     <row r="38" spans="2:16">
@@ -8397,46 +8209,46 @@
         <v>30</v>
       </c>
       <c r="C38" s="18">
-        <v>863339</v>
+        <v>884708</v>
       </c>
       <c r="D38" s="20">
-        <v>2131583</v>
+        <v>2184345</v>
       </c>
       <c r="E38" s="18">
-        <v>2451974</v>
+        <v>2450036</v>
       </c>
       <c r="F38" s="20">
         <v>5.55</v>
       </c>
       <c r="G38" s="20">
-        <v>15243689</v>
+        <v>15503633</v>
       </c>
       <c r="H38" s="20">
-        <v>8549883</v>
+        <v>8695681</v>
       </c>
       <c r="I38" s="18">
-        <v>367796</v>
+        <v>428756</v>
       </c>
       <c r="J38" s="18">
-        <v>2084178</v>
+        <v>2021280</v>
       </c>
       <c r="K38" s="19">
-        <v>0.15</v>
+        <v>0.175</v>
       </c>
       <c r="L38" s="17">
         <v>1.1</v>
       </c>
       <c r="M38" s="20">
-        <v>10681467</v>
+        <v>10880026</v>
       </c>
       <c r="N38" s="20">
-        <v>9149691</v>
+        <v>9324422</v>
       </c>
       <c r="O38" s="20">
-        <v>243550553</v>
+        <v>242515919</v>
       </c>
       <c r="P38" s="20">
-        <v>202324487</v>
+        <v>201414009</v>
       </c>
     </row>
     <row r="39" spans="2:16">
@@ -8444,46 +8256,46 @@
         <v>31</v>
       </c>
       <c r="C39" s="15">
-        <v>863189</v>
+        <v>844015</v>
       </c>
       <c r="D39" s="16">
-        <v>2131213</v>
+        <v>2083872</v>
       </c>
       <c r="E39" s="15">
-        <v>2346442</v>
+        <v>2344425</v>
       </c>
       <c r="F39" s="13">
         <v>5.54</v>
       </c>
       <c r="G39" s="16">
-        <v>14515978</v>
+        <v>14771765</v>
       </c>
       <c r="H39" s="16">
-        <v>8143659</v>
+        <v>8287159</v>
       </c>
       <c r="I39" s="15">
-        <v>344145</v>
+        <v>404413</v>
       </c>
       <c r="J39" s="15">
-        <v>2002297</v>
+        <v>1940012</v>
       </c>
       <c r="K39" s="12">
-        <v>0.1466666666666667</v>
+        <v>0.1725</v>
       </c>
       <c r="L39" s="26">
         <v>1.05</v>
       </c>
       <c r="M39" s="16">
-        <v>10274873</v>
+        <v>10371031</v>
       </c>
       <c r="N39" s="16">
-        <v>8791888</v>
+        <v>8876507</v>
       </c>
       <c r="O39" s="16">
-        <v>253825426</v>
+        <v>252886950</v>
       </c>
       <c r="P39" s="16">
-        <v>211116375</v>
+        <v>210290516</v>
       </c>
     </row>
     <row r="40" spans="2:16">
@@ -8491,46 +8303,46 @@
         <v>32</v>
       </c>
       <c r="C40" s="18">
-        <v>863039</v>
+        <v>803403</v>
       </c>
       <c r="D40" s="20">
-        <v>2130844</v>
+        <v>1983603</v>
       </c>
       <c r="E40" s="18">
-        <v>2240457</v>
+        <v>2238372</v>
       </c>
       <c r="F40" s="20">
         <v>5.52</v>
       </c>
       <c r="G40" s="20">
-        <v>13792187</v>
+        <v>14043069</v>
       </c>
       <c r="H40" s="20">
-        <v>7739440</v>
+        <v>7880221</v>
       </c>
       <c r="I40" s="18">
-        <v>321132</v>
+        <v>380523</v>
       </c>
       <c r="J40" s="18">
-        <v>1919325</v>
+        <v>1857849</v>
       </c>
       <c r="K40" s="19">
-        <v>0.1433333333333333</v>
+        <v>0.17</v>
       </c>
       <c r="L40" s="17">
         <v>1</v>
       </c>
       <c r="M40" s="20">
-        <v>9870284</v>
+        <v>9863824</v>
       </c>
       <c r="N40" s="20">
-        <v>8435850</v>
+        <v>8430165</v>
       </c>
       <c r="O40" s="20">
-        <v>263695710</v>
+        <v>262750774</v>
       </c>
       <c r="P40" s="20">
-        <v>219552225</v>
+        <v>218720681</v>
       </c>
     </row>
     <row r="41" spans="2:16">
@@ -8538,46 +8350,46 @@
         <v>33</v>
       </c>
       <c r="C41" s="15">
-        <v>862890</v>
+        <v>762866</v>
       </c>
       <c r="D41" s="16">
-        <v>2130476</v>
+        <v>1883515</v>
       </c>
       <c r="E41" s="15">
-        <v>2134077</v>
+        <v>2131934</v>
       </c>
       <c r="F41" s="13">
         <v>5.51</v>
       </c>
       <c r="G41" s="16">
-        <v>13072660</v>
+        <v>13317902</v>
       </c>
       <c r="H41" s="16">
-        <v>7337421</v>
+        <v>7475071</v>
       </c>
       <c r="I41" s="15">
-        <v>298771</v>
+        <v>357099</v>
       </c>
       <c r="J41" s="15">
-        <v>1835306</v>
+        <v>1774835</v>
       </c>
       <c r="K41" s="12">
-        <v>0.14</v>
+        <v>0.1675</v>
       </c>
       <c r="L41" s="26">
         <v>0.95</v>
       </c>
       <c r="M41" s="16">
-        <v>9467897</v>
+        <v>9358586</v>
       </c>
       <c r="N41" s="16">
-        <v>8081750</v>
+        <v>7985556</v>
       </c>
       <c r="O41" s="16">
-        <v>273163607</v>
+        <v>272109361</v>
       </c>
       <c r="P41" s="16">
-        <v>227633975</v>
+        <v>226706238</v>
       </c>
     </row>
     <row r="42" spans="2:16">
@@ -8585,46 +8397,46 @@
         <v>34</v>
       </c>
       <c r="C42" s="18">
-        <v>862741</v>
+        <v>762528</v>
       </c>
       <c r="D42" s="20">
-        <v>2130109</v>
+        <v>1882681</v>
       </c>
       <c r="E42" s="18">
-        <v>2136783</v>
+        <v>2134471</v>
       </c>
       <c r="F42" s="20">
         <v>5.49</v>
       </c>
       <c r="G42" s="20">
-        <v>13024743</v>
+        <v>13276496</v>
       </c>
       <c r="H42" s="20">
-        <v>7312262</v>
+        <v>7453599</v>
       </c>
       <c r="I42" s="18">
-        <v>292027</v>
+        <v>352188</v>
       </c>
       <c r="J42" s="18">
-        <v>1844756</v>
+        <v>1782283</v>
       </c>
       <c r="K42" s="19">
-        <v>0.1366666666666667</v>
+        <v>0.165</v>
       </c>
       <c r="L42" s="17">
         <v>0.95</v>
       </c>
       <c r="M42" s="20">
-        <v>9442370</v>
+        <v>9336280</v>
       </c>
       <c r="N42" s="20">
-        <v>8059286</v>
+        <v>7965926</v>
       </c>
       <c r="O42" s="20">
-        <v>282605978</v>
+        <v>281445641</v>
       </c>
       <c r="P42" s="20">
-        <v>235693261</v>
+        <v>234672164</v>
       </c>
     </row>
     <row r="43" spans="2:16">
@@ -8632,46 +8444,46 @@
         <v>35</v>
       </c>
       <c r="C43" s="15">
-        <v>862593</v>
+        <v>762217</v>
       </c>
       <c r="D43" s="16">
-        <v>2129742</v>
+        <v>1881913</v>
       </c>
       <c r="E43" s="15">
-        <v>2139433</v>
+        <v>2136947</v>
       </c>
       <c r="F43" s="13">
         <v>5.48</v>
       </c>
       <c r="G43" s="16">
-        <v>12976569</v>
+        <v>13234775</v>
       </c>
       <c r="H43" s="16">
-        <v>7286944</v>
+        <v>7431939</v>
       </c>
       <c r="I43" s="15">
-        <v>285258</v>
+        <v>347254</v>
       </c>
       <c r="J43" s="15">
-        <v>1854175</v>
+        <v>1789693</v>
       </c>
       <c r="K43" s="12">
-        <v>0.1333333333333333</v>
+        <v>0.1625</v>
       </c>
       <c r="L43" s="26">
         <v>0.95</v>
       </c>
       <c r="M43" s="16">
-        <v>9416686</v>
+        <v>9313852</v>
       </c>
       <c r="N43" s="16">
-        <v>8036684</v>
+        <v>7946190</v>
       </c>
       <c r="O43" s="16">
-        <v>292022664</v>
+        <v>290759492</v>
       </c>
       <c r="P43" s="16">
-        <v>243729944</v>
+        <v>242618353</v>
       </c>
     </row>
     <row r="44" spans="2:16">
@@ -8679,46 +8491,46 @@
         <v>36</v>
       </c>
       <c r="C44" s="18">
-        <v>862445</v>
+        <v>802032</v>
       </c>
       <c r="D44" s="20">
-        <v>2129376</v>
+        <v>1980217</v>
       </c>
       <c r="E44" s="18">
-        <v>2251757</v>
+        <v>2248951</v>
       </c>
       <c r="F44" s="20">
         <v>5.47</v>
       </c>
       <c r="G44" s="20">
-        <v>13590412</v>
+        <v>13868549</v>
       </c>
       <c r="H44" s="20">
-        <v>7633455</v>
+        <v>7789679</v>
       </c>
       <c r="I44" s="18">
-        <v>292728</v>
+        <v>359832</v>
       </c>
       <c r="J44" s="18">
-        <v>1959029</v>
+        <v>1889119</v>
       </c>
       <c r="K44" s="19">
-        <v>0.13</v>
+        <v>0.16</v>
       </c>
       <c r="L44" s="17">
         <v>1</v>
       </c>
       <c r="M44" s="20">
-        <v>9762831</v>
+        <v>9769896</v>
       </c>
       <c r="N44" s="20">
-        <v>8341292</v>
+        <v>8347509</v>
       </c>
       <c r="O44" s="20">
-        <v>301785495</v>
+        <v>300529388</v>
       </c>
       <c r="P44" s="20">
-        <v>252071236</v>
+        <v>250965862</v>
       </c>
     </row>
     <row r="45" spans="2:16">
@@ -8726,46 +8538,46 @@
         <v>37</v>
       </c>
       <c r="C45" s="15">
-        <v>862297</v>
+        <v>721579</v>
       </c>
       <c r="D45" s="16">
-        <v>2129011</v>
+        <v>1781579</v>
       </c>
       <c r="E45" s="15">
-        <v>2034772</v>
+        <v>2032070</v>
       </c>
       <c r="F45" s="13">
         <v>5.45</v>
       </c>
       <c r="G45" s="16">
-        <v>12220084</v>
+        <v>12477189</v>
       </c>
       <c r="H45" s="16">
-        <v>6865397</v>
+        <v>7009842</v>
       </c>
       <c r="I45" s="15">
-        <v>257738</v>
+        <v>320051</v>
       </c>
       <c r="J45" s="15">
-        <v>1777034</v>
+        <v>1712019</v>
       </c>
       <c r="K45" s="12">
-        <v>0.1266666666666666</v>
+        <v>0.1575</v>
       </c>
       <c r="L45" s="26">
         <v>0.9</v>
       </c>
       <c r="M45" s="16">
-        <v>8994409</v>
+        <v>8791421</v>
       </c>
       <c r="N45" s="16">
-        <v>7665080</v>
+        <v>7486451</v>
       </c>
       <c r="O45" s="16">
-        <v>310779904</v>
+        <v>309320809</v>
       </c>
       <c r="P45" s="16">
-        <v>259736315</v>
+        <v>258452312</v>
       </c>
     </row>
     <row r="46" spans="2:16">
@@ -8773,46 +8585,46 @@
         <v>38</v>
       </c>
       <c r="C46" s="18">
-        <v>862150</v>
+        <v>841575</v>
       </c>
       <c r="D46" s="20">
-        <v>2128647</v>
+        <v>2077848</v>
       </c>
       <c r="E46" s="18">
-        <v>2367143</v>
+        <v>2363778</v>
       </c>
       <c r="F46" s="20">
         <v>5.44</v>
       </c>
       <c r="G46" s="20">
-        <v>14145806</v>
+        <v>14451417</v>
       </c>
       <c r="H46" s="20">
-        <v>7949175</v>
+        <v>8120912</v>
       </c>
       <c r="I46" s="18">
-        <v>291948</v>
+        <v>366386</v>
       </c>
       <c r="J46" s="18">
-        <v>2075195</v>
+        <v>1997392</v>
       </c>
       <c r="K46" s="19">
-        <v>0.1233333333333334</v>
+        <v>0.155</v>
       </c>
       <c r="L46" s="17">
         <v>1.05</v>
       </c>
       <c r="M46" s="20">
-        <v>10077822</v>
+        <v>10198760</v>
       </c>
       <c r="N46" s="20">
-        <v>8618484</v>
+        <v>8724909</v>
       </c>
       <c r="O46" s="20">
-        <v>320857726</v>
+        <v>319519569</v>
       </c>
       <c r="P46" s="20">
-        <v>268354799</v>
+        <v>267177221</v>
       </c>
     </row>
     <row r="47" spans="2:16">
@@ -8820,46 +8632,46 @@
         <v>39</v>
       </c>
       <c r="C47" s="15">
-        <v>862002</v>
+        <v>801265</v>
       </c>
       <c r="D47" s="16">
-        <v>2128284</v>
+        <v>1978323</v>
       </c>
       <c r="E47" s="15">
-        <v>2259834</v>
+        <v>2256422</v>
       </c>
       <c r="F47" s="13">
         <v>5.43</v>
       </c>
       <c r="G47" s="16">
-        <v>13437608</v>
+        <v>13735612</v>
       </c>
       <c r="H47" s="16">
-        <v>7552995</v>
+        <v>7720497</v>
       </c>
       <c r="I47" s="15">
-        <v>271180</v>
+        <v>344104</v>
       </c>
       <c r="J47" s="15">
-        <v>1988654</v>
+        <v>1912318</v>
       </c>
       <c r="K47" s="12">
-        <v>0.12</v>
+        <v>0.1525</v>
       </c>
       <c r="L47" s="26">
         <v>1</v>
       </c>
       <c r="M47" s="16">
-        <v>9681279</v>
+        <v>9698820</v>
       </c>
       <c r="N47" s="16">
-        <v>8269526</v>
+        <v>8284962</v>
       </c>
       <c r="O47" s="16">
-        <v>330539005</v>
+        <v>329218389</v>
       </c>
       <c r="P47" s="16">
-        <v>276624325</v>
+        <v>275462183</v>
       </c>
     </row>
     <row r="48" spans="2:16">
@@ -8867,46 +8679,46 @@
         <v>40</v>
       </c>
       <c r="C48" s="18">
-        <v>861856</v>
+        <v>801049</v>
       </c>
       <c r="D48" s="20">
-        <v>2127922</v>
+        <v>1977790</v>
       </c>
       <c r="E48" s="18">
-        <v>2262494</v>
+        <v>2258868</v>
       </c>
       <c r="F48" s="20">
         <v>5.41</v>
       </c>
       <c r="G48" s="20">
-        <v>13386674</v>
+        <v>13691200</v>
       </c>
       <c r="H48" s="20">
-        <v>7526148</v>
+        <v>7697356</v>
       </c>
       <c r="I48" s="18">
-        <v>263958</v>
+        <v>338830</v>
       </c>
       <c r="J48" s="18">
-        <v>1998536</v>
+        <v>1920038</v>
       </c>
       <c r="K48" s="19">
-        <v>0.1166666666666667</v>
+        <v>0.15</v>
       </c>
       <c r="L48" s="17">
         <v>1</v>
       </c>
       <c r="M48" s="20">
-        <v>9654069</v>
+        <v>9675146</v>
       </c>
       <c r="N48" s="20">
-        <v>8245581</v>
+        <v>8264128</v>
       </c>
       <c r="O48" s="20">
-        <v>340193075</v>
+        <v>338893535</v>
       </c>
       <c r="P48" s="20">
-        <v>284869906</v>
+        <v>283726311</v>
       </c>
     </row>
     <row r="49" spans="2:16">
@@ -8914,46 +8726,46 @@
         <v>41</v>
       </c>
       <c r="C49" s="15">
-        <v>861709</v>
+        <v>840893</v>
       </c>
       <c r="D49" s="16">
-        <v>2127560</v>
+        <v>2076164</v>
       </c>
       <c r="E49" s="15">
-        <v>2375525</v>
+        <v>2371487</v>
       </c>
       <c r="F49" s="13">
         <v>5.4</v>
       </c>
       <c r="G49" s="16">
-        <v>13985627</v>
+        <v>14311749</v>
       </c>
       <c r="H49" s="16">
-        <v>7864747</v>
+        <v>8048140</v>
       </c>
       <c r="I49" s="15">
-        <v>269226</v>
+        <v>349794</v>
       </c>
       <c r="J49" s="15">
-        <v>2106299</v>
+        <v>2021693</v>
       </c>
       <c r="K49" s="12">
-        <v>0.1133333333333333</v>
+        <v>0.1475</v>
       </c>
       <c r="L49" s="26">
         <v>1.05</v>
       </c>
       <c r="M49" s="16">
-        <v>9992307</v>
+        <v>10124304</v>
       </c>
       <c r="N49" s="16">
-        <v>8543230</v>
+        <v>8659388</v>
       </c>
       <c r="O49" s="16">
-        <v>350185382</v>
+        <v>349017839</v>
       </c>
       <c r="P49" s="16">
-        <v>293413136</v>
+        <v>292385699</v>
       </c>
     </row>
     <row r="50" spans="2:16">
@@ -8961,46 +8773,46 @@
         <v>42</v>
       </c>
       <c r="C50" s="18">
-        <v>861563</v>
+        <v>880734</v>
       </c>
       <c r="D50" s="20">
-        <v>2127199</v>
+        <v>2174533</v>
       </c>
       <c r="E50" s="18">
-        <v>2488813</v>
+        <v>2484333</v>
       </c>
       <c r="F50" s="20">
         <v>5.38</v>
       </c>
       <c r="G50" s="20">
-        <v>14579716</v>
+        <v>14928010</v>
       </c>
       <c r="H50" s="20">
-        <v>8200770</v>
+        <v>8396677</v>
       </c>
       <c r="I50" s="18">
-        <v>273769</v>
+        <v>360228</v>
       </c>
       <c r="J50" s="18">
-        <v>2215044</v>
+        <v>2124105</v>
       </c>
       <c r="K50" s="19">
-        <v>0.11</v>
+        <v>0.145</v>
       </c>
       <c r="L50" s="17">
         <v>1.1</v>
       </c>
       <c r="M50" s="20">
-        <v>10327969</v>
+        <v>10571210</v>
       </c>
       <c r="N50" s="20">
-        <v>8838613</v>
+        <v>9052665</v>
       </c>
       <c r="O50" s="20">
-        <v>360513351</v>
+        <v>359589049</v>
       </c>
       <c r="P50" s="20">
-        <v>302251749</v>
+        <v>301438363</v>
       </c>
     </row>
     <row r="51" spans="2:16">
@@ -9008,46 +8820,46 @@
         <v>43</v>
       </c>
       <c r="C51" s="15">
-        <v>861417</v>
+        <v>840524</v>
       </c>
       <c r="D51" s="16">
-        <v>2126840</v>
+        <v>2075254</v>
       </c>
       <c r="E51" s="15">
-        <v>2381073</v>
+        <v>2376553</v>
       </c>
       <c r="F51" s="13">
         <v>5.37</v>
       </c>
       <c r="G51" s="16">
-        <v>13879105</v>
+        <v>14218648</v>
       </c>
       <c r="H51" s="16">
-        <v>7808537</v>
+        <v>7999568</v>
       </c>
       <c r="I51" s="15">
-        <v>253981</v>
+        <v>338659</v>
       </c>
       <c r="J51" s="15">
-        <v>2127092</v>
+        <v>2037894</v>
       </c>
       <c r="K51" s="12">
-        <v>0.1066666666666667</v>
+        <v>0.1425</v>
       </c>
       <c r="L51" s="26">
         <v>1.05</v>
       </c>
       <c r="M51" s="16">
-        <v>9935377</v>
+        <v>10074822</v>
       </c>
       <c r="N51" s="16">
-        <v>8493132</v>
+        <v>8615843</v>
       </c>
       <c r="O51" s="16">
-        <v>370448728</v>
+        <v>369663871</v>
       </c>
       <c r="P51" s="16">
-        <v>310744881</v>
+        <v>310054207</v>
       </c>
     </row>
     <row r="52" spans="2:16">
@@ -9055,46 +8867,46 @@
         <v>44</v>
       </c>
       <c r="C52" s="18">
-        <v>861272</v>
+        <v>800344</v>
       </c>
       <c r="D52" s="20">
-        <v>2126480</v>
+        <v>1976050</v>
       </c>
       <c r="E52" s="18">
-        <v>2273067</v>
+        <v>2268523</v>
       </c>
       <c r="F52" s="20">
         <v>5.36</v>
       </c>
       <c r="G52" s="20">
-        <v>13183482</v>
+        <v>13513603</v>
       </c>
       <c r="H52" s="20">
-        <v>7418926</v>
+        <v>7604700</v>
       </c>
       <c r="I52" s="18">
-        <v>234884</v>
+        <v>317593</v>
       </c>
       <c r="J52" s="18">
-        <v>2038183</v>
+        <v>1950930</v>
       </c>
       <c r="K52" s="19">
-        <v>0.1033333333333333</v>
+        <v>0.14</v>
       </c>
       <c r="L52" s="17">
         <v>1</v>
       </c>
       <c r="M52" s="20">
-        <v>9545406</v>
+        <v>9580750</v>
       </c>
       <c r="N52" s="20">
-        <v>8149957</v>
+        <v>8181060</v>
       </c>
       <c r="O52" s="20">
-        <v>379994134</v>
+        <v>379244621</v>
       </c>
       <c r="P52" s="20">
-        <v>318894838</v>
+        <v>318235266</v>
       </c>
     </row>
     <row r="53" spans="2:16">
@@ -9102,46 +8914,46 @@
         <v>45</v>
       </c>
       <c r="C53" s="15">
-        <v>861127</v>
+        <v>760192</v>
       </c>
       <c r="D53" s="16">
-        <v>2126122</v>
+        <v>1876913</v>
       </c>
       <c r="E53" s="15">
-        <v>2164794</v>
+        <v>2160246</v>
       </c>
       <c r="F53" s="13">
         <v>5.34</v>
       </c>
       <c r="G53" s="16">
-        <v>12492840</v>
+        <v>12812886</v>
       </c>
       <c r="H53" s="16">
-        <v>7031933</v>
+        <v>7212079</v>
       </c>
       <c r="I53" s="15">
-        <v>216479</v>
+        <v>297034</v>
       </c>
       <c r="J53" s="15">
-        <v>1948315</v>
+        <v>1863212</v>
       </c>
       <c r="K53" s="12">
-        <v>0.1</v>
+        <v>0.1375</v>
       </c>
       <c r="L53" s="26">
         <v>0.95</v>
       </c>
       <c r="M53" s="16">
-        <v>9158055</v>
+        <v>9088993</v>
       </c>
       <c r="N53" s="16">
-        <v>7809088</v>
+        <v>7748314</v>
       </c>
       <c r="O53" s="16">
-        <v>389152189</v>
+        <v>388333614</v>
       </c>
       <c r="P53" s="16">
-        <v>326703926</v>
+        <v>325983580</v>
       </c>
     </row>
     <row r="54" spans="2:16">
@@ -9149,46 +8961,46 @@
         <v>46</v>
       </c>
       <c r="C54" s="18">
-        <v>860982</v>
+        <v>760067</v>
       </c>
       <c r="D54" s="20">
-        <v>2125765</v>
+        <v>1876606</v>
       </c>
       <c r="E54" s="18">
-        <v>2167294</v>
+        <v>2162507</v>
       </c>
       <c r="F54" s="20">
         <v>5.33</v>
       </c>
       <c r="G54" s="20">
-        <v>12475560</v>
+        <v>12770731</v>
       </c>
       <c r="H54" s="20">
-        <v>7023865</v>
+        <v>7190049</v>
       </c>
       <c r="I54" s="18">
-        <v>216729</v>
+        <v>291938</v>
       </c>
       <c r="J54" s="18">
-        <v>1950565</v>
+        <v>1870569</v>
       </c>
       <c r="K54" s="19">
-        <v>0.1</v>
+        <v>0.135</v>
       </c>
       <c r="L54" s="17">
         <v>0.95</v>
       </c>
       <c r="M54" s="20">
-        <v>9149630</v>
+        <v>9066655</v>
       </c>
       <c r="N54" s="20">
-        <v>7801674</v>
+        <v>7728657</v>
       </c>
       <c r="O54" s="20">
-        <v>398301819</v>
+        <v>397400269</v>
       </c>
       <c r="P54" s="20">
-        <v>334505600</v>
+        <v>333712237</v>
       </c>
     </row>
     <row r="55" spans="2:16">
@@ -9196,46 +9008,46 @@
         <v>47</v>
       </c>
       <c r="C55" s="15">
-        <v>860838</v>
+        <v>759953</v>
       </c>
       <c r="D55" s="16">
-        <v>2125408</v>
+        <v>1876323</v>
       </c>
       <c r="E55" s="15">
-        <v>2169792</v>
+        <v>2164762</v>
       </c>
       <c r="F55" s="13">
         <v>5.32</v>
       </c>
       <c r="G55" s="16">
-        <v>12458278</v>
+        <v>12728623</v>
       </c>
       <c r="H55" s="16">
-        <v>7015791</v>
+        <v>7168034</v>
       </c>
       <c r="I55" s="15">
-        <v>216979</v>
+        <v>286831</v>
       </c>
       <c r="J55" s="15">
-        <v>1952813</v>
+        <v>1877931</v>
       </c>
       <c r="K55" s="12">
-        <v>0.1</v>
+        <v>0.1325</v>
       </c>
       <c r="L55" s="26">
         <v>0.95</v>
       </c>
       <c r="M55" s="16">
-        <v>9141200</v>
+        <v>9044357</v>
       </c>
       <c r="N55" s="16">
-        <v>7794256</v>
+        <v>7709034</v>
       </c>
       <c r="O55" s="16">
-        <v>407443018</v>
+        <v>406444626</v>
       </c>
       <c r="P55" s="16">
-        <v>342299856</v>
+        <v>341421271</v>
       </c>
     </row>
     <row r="56" spans="2:16">
@@ -9243,46 +9055,46 @@
         <v>48</v>
       </c>
       <c r="C56" s="18">
-        <v>860694</v>
+        <v>799839</v>
       </c>
       <c r="D56" s="20">
-        <v>2125053</v>
+        <v>1974803</v>
       </c>
       <c r="E56" s="18">
-        <v>2283589</v>
+        <v>2278032</v>
       </c>
       <c r="F56" s="20">
         <v>5.3</v>
       </c>
       <c r="G56" s="20">
-        <v>13078426</v>
+        <v>13336522</v>
       </c>
       <c r="H56" s="20">
-        <v>7366762</v>
+        <v>7512141</v>
       </c>
       <c r="I56" s="18">
-        <v>228359</v>
+        <v>296144</v>
       </c>
       <c r="J56" s="18">
-        <v>2055230</v>
+        <v>1981888</v>
       </c>
       <c r="K56" s="19">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="L56" s="17">
         <v>1</v>
       </c>
       <c r="M56" s="20">
-        <v>9491815</v>
+        <v>9486944</v>
       </c>
       <c r="N56" s="20">
-        <v>8102797</v>
+        <v>8098510</v>
       </c>
       <c r="O56" s="20">
-        <v>416934833</v>
+        <v>415931570</v>
       </c>
       <c r="P56" s="20">
-        <v>350402653</v>
+        <v>349519781</v>
       </c>
     </row>
     <row r="57" spans="2:16">
@@ -9290,46 +9102,46 @@
         <v>49</v>
       </c>
       <c r="C57" s="15">
-        <v>860550</v>
+        <v>719763</v>
       </c>
       <c r="D57" s="16">
-        <v>2124698</v>
+        <v>1777096</v>
       </c>
       <c r="E57" s="15">
-        <v>2063355</v>
+        <v>2058111</v>
       </c>
       <c r="F57" s="13">
         <v>5.29</v>
       </c>
       <c r="G57" s="16">
-        <v>11787156</v>
+        <v>11996700</v>
       </c>
       <c r="H57" s="16">
-        <v>6640987</v>
+        <v>6759046</v>
       </c>
       <c r="I57" s="15">
-        <v>206336</v>
+        <v>262409</v>
       </c>
       <c r="J57" s="15">
-        <v>1857020</v>
+        <v>1795702</v>
       </c>
       <c r="K57" s="12">
-        <v>0.1</v>
+        <v>0.1275</v>
       </c>
       <c r="L57" s="26">
         <v>0.9</v>
       </c>
       <c r="M57" s="16">
-        <v>8765685</v>
+        <v>8536142</v>
       </c>
       <c r="N57" s="16">
-        <v>7463803</v>
+        <v>7261805</v>
       </c>
       <c r="O57" s="16">
-        <v>425700518</v>
+        <v>424467711</v>
       </c>
       <c r="P57" s="16">
-        <v>357866455</v>
+        <v>356781586</v>
       </c>
     </row>
     <row r="58" spans="2:16">
@@ -9337,46 +9149,46 @@
         <v>50</v>
       </c>
       <c r="C58" s="18">
-        <v>860406</v>
+        <v>839625</v>
       </c>
       <c r="D58" s="20">
-        <v>2124344</v>
+        <v>2073034</v>
       </c>
       <c r="E58" s="18">
-        <v>2400406</v>
+        <v>2394001</v>
       </c>
       <c r="F58" s="20">
         <v>5.28</v>
       </c>
       <c r="G58" s="20">
-        <v>13677841</v>
+        <v>13893958</v>
       </c>
       <c r="H58" s="20">
-        <v>7708033</v>
+        <v>7829824</v>
       </c>
       <c r="I58" s="18">
-        <v>240041</v>
+        <v>299250</v>
       </c>
       <c r="J58" s="18">
-        <v>2160365</v>
+        <v>2094751</v>
       </c>
       <c r="K58" s="19">
-        <v>0.1</v>
+        <v>0.125</v>
       </c>
       <c r="L58" s="17">
         <v>1.05</v>
       </c>
       <c r="M58" s="20">
-        <v>9832377</v>
+        <v>9902859</v>
       </c>
       <c r="N58" s="20">
-        <v>8402491</v>
+        <v>8464516</v>
       </c>
       <c r="O58" s="20">
-        <v>435532894</v>
+        <v>434370570</v>
       </c>
       <c r="P58" s="20">
-        <v>366268947</v>
+        <v>365246102</v>
       </c>
     </row>
     <row r="59" spans="2:16">
@@ -9384,46 +9196,46 @@
         <v>51</v>
       </c>
       <c r="C59" s="15">
-        <v>860263</v>
+        <v>799557</v>
       </c>
       <c r="D59" s="16">
-        <v>2123990</v>
+        <v>1974105</v>
       </c>
       <c r="E59" s="15">
-        <v>2291470</v>
+        <v>2285089</v>
       </c>
       <c r="F59" s="13">
         <v>5.26</v>
       </c>
       <c r="G59" s="16">
-        <v>13024009</v>
+        <v>13204202</v>
       </c>
       <c r="H59" s="16">
-        <v>7341302</v>
+        <v>7442872</v>
       </c>
       <c r="I59" s="15">
-        <v>229147</v>
+        <v>279923</v>
       </c>
       <c r="J59" s="15">
-        <v>2062323</v>
+        <v>2005166</v>
       </c>
       <c r="K59" s="12">
-        <v>0.1</v>
+        <v>0.1225</v>
       </c>
       <c r="L59" s="26">
         <v>1</v>
       </c>
       <c r="M59" s="16">
-        <v>9465292</v>
+        <v>9416977</v>
       </c>
       <c r="N59" s="16">
-        <v>8079457</v>
+        <v>8036940</v>
       </c>
       <c r="O59" s="16">
-        <v>444998187</v>
+        <v>443787548</v>
       </c>
       <c r="P59" s="16">
-        <v>374348404</v>
+        <v>373283042</v>
       </c>
     </row>
     <row r="60" spans="2:16">
@@ -9431,46 +9243,46 @@
         <v>52</v>
       </c>
       <c r="C60" s="18">
-        <v>860121</v>
+        <v>799477</v>
       </c>
       <c r="D60" s="20">
-        <v>2123638</v>
+        <v>1973909</v>
       </c>
       <c r="E60" s="18">
-        <v>2294096</v>
+        <v>2287429</v>
       </c>
       <c r="F60" s="20">
         <v>5.25</v>
       </c>
       <c r="G60" s="20">
-        <v>13005880</v>
+        <v>13160199</v>
       </c>
       <c r="H60" s="20">
-        <v>7332811</v>
+        <v>7419817</v>
       </c>
       <c r="I60" s="18">
-        <v>229410</v>
+        <v>274491</v>
       </c>
       <c r="J60" s="18">
-        <v>2064686</v>
+        <v>2012938</v>
       </c>
       <c r="K60" s="19">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="L60" s="17">
         <v>1</v>
       </c>
       <c r="M60" s="20">
-        <v>9456449</v>
+        <v>9393726</v>
       </c>
       <c r="N60" s="20">
-        <v>8071675</v>
+        <v>8016479</v>
       </c>
       <c r="O60" s="20">
-        <v>454454636</v>
+        <v>453181274</v>
       </c>
       <c r="P60" s="20">
-        <v>382420079</v>
+        <v>381299521</v>
       </c>
     </row>
     <row r="61" spans="2:16">
@@ -9478,46 +9290,46 @@
         <v>53</v>
       </c>
       <c r="C61" s="15">
-        <v>859978</v>
+        <v>839374</v>
       </c>
       <c r="D61" s="16">
-        <v>2123286</v>
+        <v>2072414</v>
       </c>
       <c r="E61" s="15">
-        <v>2408678</v>
+        <v>2401371</v>
       </c>
       <c r="F61" s="13">
         <v>5.24</v>
       </c>
       <c r="G61" s="16">
-        <v>13620861</v>
+        <v>13755568</v>
       </c>
       <c r="H61" s="16">
-        <v>7681351</v>
+        <v>7757318</v>
       </c>
       <c r="I61" s="15">
-        <v>240868</v>
+        <v>282161</v>
       </c>
       <c r="J61" s="15">
-        <v>2167810</v>
+        <v>2119210</v>
       </c>
       <c r="K61" s="12">
-        <v>0.1</v>
+        <v>0.1175</v>
       </c>
       <c r="L61" s="26">
         <v>1.05</v>
       </c>
       <c r="M61" s="16">
-        <v>9804638</v>
+        <v>9829732</v>
       </c>
       <c r="N61" s="16">
-        <v>8378081</v>
+        <v>8400164</v>
       </c>
       <c r="O61" s="16">
-        <v>464259273</v>
+        <v>463011006</v>
       </c>
       <c r="P61" s="16">
-        <v>390798161</v>
+        <v>389699685</v>
       </c>
     </row>
     <row r="62" spans="2:16">
@@ -9525,46 +9337,46 @@
         <v>54</v>
       </c>
       <c r="C62" s="18">
-        <v>859836</v>
+        <v>879270</v>
       </c>
       <c r="D62" s="20">
-        <v>2122935</v>
+        <v>2170918</v>
       </c>
       <c r="E62" s="18">
-        <v>2523523</v>
+        <v>2515539</v>
       </c>
       <c r="F62" s="20">
         <v>5.22</v>
       </c>
       <c r="G62" s="20">
-        <v>14234120</v>
+        <v>14346744</v>
       </c>
       <c r="H62" s="20">
-        <v>8029083</v>
+        <v>8092611</v>
       </c>
       <c r="I62" s="18">
-        <v>252352</v>
+        <v>289287</v>
       </c>
       <c r="J62" s="18">
-        <v>2271171</v>
+        <v>2226252</v>
       </c>
       <c r="K62" s="19">
-        <v>0.1</v>
+        <v>0.115</v>
       </c>
       <c r="L62" s="17">
         <v>1.1</v>
       </c>
       <c r="M62" s="20">
-        <v>10152019</v>
+        <v>10263529</v>
       </c>
       <c r="N62" s="20">
-        <v>8683776</v>
+        <v>8781905</v>
       </c>
       <c r="O62" s="20">
-        <v>474411292</v>
+        <v>473274535</v>
       </c>
       <c r="P62" s="20">
-        <v>399481937</v>
+        <v>398481590</v>
       </c>
     </row>
     <row r="63" spans="2:16">
@@ -9572,46 +9384,46 @@
         <v>55</v>
       </c>
       <c r="C63" s="15">
-        <v>859694</v>
+        <v>839238</v>
       </c>
       <c r="D63" s="16">
-        <v>2122585</v>
+        <v>2072079</v>
       </c>
       <c r="E63" s="15">
-        <v>2414192</v>
+        <v>2406252</v>
       </c>
       <c r="F63" s="13">
         <v>5.21</v>
       </c>
       <c r="G63" s="16">
-        <v>13582911</v>
+        <v>13663590</v>
       </c>
       <c r="H63" s="16">
-        <v>7663557</v>
+        <v>7709077</v>
       </c>
       <c r="I63" s="15">
-        <v>241419</v>
+        <v>270703</v>
       </c>
       <c r="J63" s="15">
-        <v>2172773</v>
+        <v>2135549</v>
       </c>
       <c r="K63" s="12">
-        <v>0.1</v>
+        <v>0.1125</v>
       </c>
       <c r="L63" s="26">
         <v>1.05</v>
       </c>
       <c r="M63" s="16">
-        <v>9786143</v>
+        <v>9781156</v>
       </c>
       <c r="N63" s="16">
-        <v>8361806</v>
+        <v>8357417</v>
       </c>
       <c r="O63" s="16">
-        <v>484197435</v>
+        <v>483055690</v>
       </c>
       <c r="P63" s="16">
-        <v>407843743</v>
+        <v>406839008</v>
       </c>
     </row>
     <row r="64" spans="2:16">
@@ -9619,46 +9431,46 @@
         <v>56</v>
       </c>
       <c r="C64" s="18">
-        <v>859553</v>
+        <v>799217</v>
       </c>
       <c r="D64" s="20">
-        <v>2122236</v>
+        <v>1973268</v>
       </c>
       <c r="E64" s="18">
-        <v>2304599</v>
+        <v>2296727</v>
       </c>
       <c r="F64" s="20">
         <v>5.2</v>
       </c>
       <c r="G64" s="20">
-        <v>12933438</v>
+        <v>12984736</v>
       </c>
       <c r="H64" s="20">
-        <v>7298838</v>
+        <v>7327788</v>
       </c>
       <c r="I64" s="18">
-        <v>230460</v>
+        <v>252640</v>
       </c>
       <c r="J64" s="18">
-        <v>2074139</v>
+        <v>2044087</v>
       </c>
       <c r="K64" s="19">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="L64" s="17">
         <v>1</v>
       </c>
       <c r="M64" s="20">
-        <v>9421075</v>
+        <v>9301055</v>
       </c>
       <c r="N64" s="20">
-        <v>8040546</v>
+        <v>7934929</v>
       </c>
       <c r="O64" s="20">
-        <v>493618509</v>
+        <v>492356746</v>
       </c>
       <c r="P64" s="20">
-        <v>415884288</v>
+        <v>414773936</v>
       </c>
     </row>
     <row r="65" spans="2:16">
@@ -9666,46 +9478,46 @@
         <v>57</v>
       </c>
       <c r="C65" s="15">
-        <v>859412</v>
+        <v>759207</v>
       </c>
       <c r="D65" s="16">
-        <v>2121888</v>
+        <v>1874481</v>
       </c>
       <c r="E65" s="15">
-        <v>2194743</v>
+        <v>2186964</v>
       </c>
       <c r="F65" s="13">
         <v>5.18</v>
       </c>
       <c r="G65" s="16">
-        <v>12285701</v>
+        <v>12310172</v>
       </c>
       <c r="H65" s="16">
-        <v>6934926</v>
+        <v>6948739</v>
       </c>
       <c r="I65" s="15">
-        <v>219474</v>
+        <v>235099</v>
       </c>
       <c r="J65" s="15">
-        <v>1975269</v>
+        <v>1951865</v>
       </c>
       <c r="K65" s="12">
-        <v>0.1</v>
+        <v>0.1075</v>
       </c>
       <c r="L65" s="26">
         <v>0.95</v>
       </c>
       <c r="M65" s="16">
-        <v>9056814</v>
+        <v>8823220</v>
       </c>
       <c r="N65" s="16">
-        <v>7719996</v>
+        <v>7514434</v>
       </c>
       <c r="O65" s="16">
-        <v>502675324</v>
+        <v>501179966</v>
       </c>
       <c r="P65" s="16">
-        <v>423604285</v>
+        <v>422288370</v>
       </c>
     </row>
     <row r="66" spans="2:16">
@@ -9713,46 +9525,46 @@
         <v>58</v>
       </c>
       <c r="C66" s="18">
-        <v>859271</v>
+        <v>759161</v>
       </c>
       <c r="D66" s="20">
-        <v>2121540</v>
+        <v>1874368</v>
       </c>
       <c r="E66" s="18">
-        <v>2197237</v>
+        <v>2189153</v>
       </c>
       <c r="F66" s="20">
         <v>5.17</v>
       </c>
       <c r="G66" s="20">
-        <v>12268482</v>
+        <v>12268614</v>
       </c>
       <c r="H66" s="20">
-        <v>6926835</v>
+        <v>6926910</v>
       </c>
       <c r="I66" s="18">
-        <v>219724</v>
+        <v>229861</v>
       </c>
       <c r="J66" s="18">
-        <v>1977513</v>
+        <v>1959292</v>
       </c>
       <c r="K66" s="19">
-        <v>0.1</v>
+        <v>0.105</v>
       </c>
       <c r="L66" s="17">
         <v>0.95</v>
       </c>
       <c r="M66" s="20">
-        <v>9048375</v>
+        <v>8801277</v>
       </c>
       <c r="N66" s="20">
-        <v>7712570</v>
+        <v>7495124</v>
       </c>
       <c r="O66" s="20">
-        <v>511723699</v>
+        <v>509981244</v>
       </c>
       <c r="P66" s="20">
-        <v>431316855</v>
+        <v>429783494</v>
       </c>
     </row>
     <row r="67" spans="2:16">
@@ -9760,46 +9572,46 @@
         <v>59</v>
       </c>
       <c r="C67" s="15">
-        <v>859131</v>
+        <v>759119</v>
       </c>
       <c r="D67" s="16">
-        <v>2121193</v>
+        <v>1874264</v>
       </c>
       <c r="E67" s="15">
-        <v>2199731</v>
+        <v>2191335</v>
       </c>
       <c r="F67" s="13">
         <v>5.16</v>
       </c>
       <c r="G67" s="16">
-        <v>12251270</v>
+        <v>12227114</v>
       </c>
       <c r="H67" s="16">
-        <v>6918743</v>
+        <v>6905101</v>
       </c>
       <c r="I67" s="15">
-        <v>219973</v>
+        <v>224612</v>
       </c>
       <c r="J67" s="15">
-        <v>1979758</v>
+        <v>1966723</v>
       </c>
       <c r="K67" s="12">
-        <v>0.1</v>
+        <v>0.1025</v>
       </c>
       <c r="L67" s="26">
         <v>0.95</v>
       </c>
       <c r="M67" s="16">
-        <v>9039937</v>
+        <v>8779365</v>
       </c>
       <c r="N67" s="16">
-        <v>7705144</v>
+        <v>7475841</v>
       </c>
       <c r="O67" s="16">
-        <v>520763635</v>
+        <v>518760608</v>
       </c>
       <c r="P67" s="16">
-        <v>439021999</v>
+        <v>437259335</v>
       </c>
     </row>
     <row r="68" spans="2:16">
@@ -9807,28 +9619,28 @@
         <v>60</v>
       </c>
       <c r="C68" s="18">
-        <v>858990</v>
+        <v>799031</v>
       </c>
       <c r="D68" s="20">
-        <v>2120848</v>
+        <v>1972808</v>
       </c>
       <c r="E68" s="18">
-        <v>2315100</v>
+        <v>2305929</v>
       </c>
       <c r="F68" s="20">
         <v>5.14</v>
       </c>
       <c r="G68" s="20">
-        <v>12861124</v>
+        <v>12810178</v>
       </c>
       <c r="H68" s="20">
-        <v>7264857</v>
+        <v>7236079</v>
       </c>
       <c r="I68" s="18">
-        <v>231510</v>
+        <v>230593</v>
       </c>
       <c r="J68" s="18">
-        <v>2083590</v>
+        <v>2075336</v>
       </c>
       <c r="K68" s="19">
         <v>0.1</v>
@@ -9837,16 +9649,16 @@
         <v>1</v>
       </c>
       <c r="M68" s="20">
-        <v>9385704</v>
+        <v>9208887</v>
       </c>
       <c r="N68" s="20">
-        <v>8009420</v>
+        <v>7853820</v>
       </c>
       <c r="O68" s="20">
-        <v>530149339</v>
+        <v>527969495</v>
       </c>
       <c r="P68" s="20">
-        <v>447031419</v>
+        <v>445113156</v>
       </c>
     </row>
   </sheetData>
@@ -9883,7 +9695,7 @@
   <sheetData>
     <row r="2" spans="2:5">
       <c r="B2" s="1" t="s">
-        <v>178</v>
+        <v>162</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -9891,7 +9703,7 @@
     </row>
     <row r="4" spans="2:5">
       <c r="B4" s="3" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
@@ -9899,130 +9711,130 @@
     </row>
     <row r="5" spans="2:5">
       <c r="C5" s="10" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="D5" s="25" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6" spans="2:5">
       <c r="B6" s="4" t="s">
-        <v>158</v>
+        <v>142</v>
       </c>
       <c r="C6" s="16">
-        <v>17596785</v>
+        <v>15996303</v>
       </c>
       <c r="D6" s="16">
-        <v>39525368</v>
+        <v>39715677</v>
       </c>
       <c r="E6" s="16">
-        <v>86473527</v>
+        <v>79290399</v>
       </c>
     </row>
     <row r="7" spans="2:5">
       <c r="B7" s="4" t="s">
-        <v>180</v>
+        <v>164</v>
       </c>
       <c r="C7" s="16">
-        <v>362934837</v>
+        <v>334142170</v>
       </c>
       <c r="D7" s="16">
-        <v>530149339</v>
+        <v>527969495</v>
       </c>
       <c r="E7" s="16">
-        <v>766250097</v>
+        <v>712834365</v>
       </c>
     </row>
     <row r="8" spans="2:5">
       <c r="B8" s="4" t="s">
-        <v>181</v>
+        <v>165</v>
       </c>
       <c r="C8" s="16">
-        <v>235906954</v>
+        <v>218040747</v>
       </c>
       <c r="D8" s="16">
-        <v>402257723</v>
+        <v>407706706</v>
       </c>
       <c r="E8" s="16">
-        <v>637936115</v>
+        <v>589450553</v>
       </c>
     </row>
     <row r="9" spans="2:5">
       <c r="B9" s="4" t="s">
-        <v>182</v>
+        <v>166</v>
       </c>
       <c r="C9" s="16">
-        <v>127027883</v>
+        <v>116101423</v>
       </c>
       <c r="D9" s="16">
-        <v>127891616</v>
+        <v>120262789</v>
       </c>
       <c r="E9" s="16">
-        <v>128313982</v>
+        <v>123383813</v>
       </c>
     </row>
     <row r="10" spans="2:5">
       <c r="B10" s="4" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
       <c r="C10" s="16">
-        <v>307682657</v>
+        <v>282345110</v>
       </c>
       <c r="D10" s="16">
-        <v>447031419</v>
+        <v>445113156</v>
       </c>
       <c r="E10" s="16">
-        <v>645050086</v>
+        <v>598044242</v>
       </c>
     </row>
     <row r="11" spans="2:5">
       <c r="B11" s="4" t="s">
-        <v>183</v>
+        <v>167</v>
       </c>
       <c r="C11" s="12">
-        <v>0.4575461142899558</v>
+        <v>0.4759121156776943</v>
       </c>
       <c r="D11" s="12">
-        <v>0.6629847987893773</v>
+        <v>0.6739879077755397</v>
       </c>
       <c r="E11" s="12">
-        <v>0.7549464960554249</v>
+        <v>0.7606800668006904</v>
       </c>
     </row>
     <row r="12" spans="2:5">
       <c r="B12" s="4" t="s">
-        <v>184</v>
+        <v>168</v>
       </c>
       <c r="C12" s="12">
-        <v>0.5919607653685717</v>
+        <v>0.6156920824992982</v>
       </c>
       <c r="D12" s="12">
-        <v>0.7186124681040679</v>
+        <v>0.7319379453501687</v>
       </c>
       <c r="E12" s="12">
-        <v>0.7659360557910311</v>
+        <v>0.7733928036110551</v>
       </c>
     </row>
     <row r="13" spans="2:5">
       <c r="B13" s="4" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="C13" s="12">
-        <v>0.31</v>
+        <v>0.17</v>
       </c>
       <c r="D13" s="12">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="E13" s="12">
-        <v>0.46</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="14" spans="2:5">
       <c r="B14" s="4" t="s">
-        <v>161</v>
+        <v>145</v>
       </c>
       <c r="C14" s="12">
         <v>0.5010028863558533</v>
@@ -10036,21 +9848,21 @@
     </row>
     <row r="15" spans="2:5">
       <c r="B15" s="4" t="s">
-        <v>186</v>
+        <v>170</v>
       </c>
       <c r="C15" s="12">
-        <v>0.02261099476620821</v>
+        <v>0.07504697028914474</v>
       </c>
       <c r="D15" s="12">
-        <v>0.01019659176414058</v>
+        <v>0.04921944524678067</v>
       </c>
       <c r="E15" s="12">
-        <v>0.004025633167346054</v>
+        <v>0.03039200718336591</v>
       </c>
     </row>
     <row r="16" spans="2:5">
       <c r="B16" s="4" t="s">
-        <v>187</v>
+        <v>171</v>
       </c>
       <c r="C16" s="12">
         <v>0.356</v>
@@ -10064,7 +9876,7 @@
     </row>
     <row r="17" spans="2:5">
       <c r="B17" s="4" t="s">
-        <v>188</v>
+        <v>172</v>
       </c>
       <c r="C17" s="16">
         <v>11700000</v>
@@ -10090,7 +9902,7 @@
   <sheetPr>
     <tabColor rgb="FF6366F1"/>
   </sheetPr>
-  <dimension ref="B2:E58"/>
+  <dimension ref="B2:E55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="3.7109375" customWidth="1"/>
@@ -10102,7 +9914,7 @@
   <sheetData>
     <row r="2" spans="2:5">
       <c r="B2" s="1" t="s">
-        <v>189</v>
+        <v>173</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -10110,7 +9922,7 @@
     </row>
     <row r="3" spans="2:5">
       <c r="B3" s="2" t="s">
-        <v>190</v>
+        <v>174</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -10118,42 +9930,42 @@
     </row>
     <row r="5" spans="2:5">
       <c r="B5" s="4" t="s">
-        <v>191</v>
+        <v>175</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>192</v>
+        <v>176</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>193</v>
+        <v>177</v>
       </c>
     </row>
     <row r="6" spans="2:5">
       <c r="C6" s="28" t="s">
-        <v>194</v>
+        <v>178</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>195</v>
+        <v>179</v>
       </c>
     </row>
     <row r="7" spans="2:5">
       <c r="C7" s="29" t="s">
-        <v>196</v>
+        <v>180</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
     </row>
     <row r="8" spans="2:5">
       <c r="C8" s="30" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>199</v>
+        <v>183</v>
       </c>
     </row>
     <row r="10" spans="2:5">
       <c r="B10" s="3" t="s">
-        <v>200</v>
+        <v>184</v>
       </c>
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
@@ -10161,16 +9973,16 @@
     </row>
     <row r="11" spans="2:5">
       <c r="B11" s="10" t="s">
-        <v>201</v>
+        <v>185</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>204</v>
+        <v>188</v>
       </c>
     </row>
     <row r="12" spans="2:5">
@@ -10178,186 +9990,186 @@
         <v>15</v>
       </c>
       <c r="C12" s="27" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>206</v>
+        <v>190</v>
       </c>
       <c r="E12" s="27" t="s">
-        <v>192</v>
+        <v>176</v>
       </c>
     </row>
     <row r="13" spans="2:5">
       <c r="B13" s="4" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>207</v>
+        <v>191</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>208</v>
+        <v>192</v>
       </c>
       <c r="E13" s="27" t="s">
-        <v>192</v>
+        <v>176</v>
       </c>
     </row>
     <row r="14" spans="2:5">
       <c r="B14" s="4" t="s">
-        <v>209</v>
+        <v>193</v>
       </c>
       <c r="C14" s="27" t="s">
-        <v>210</v>
+        <v>194</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>211</v>
+        <v>195</v>
       </c>
       <c r="E14" s="27" t="s">
-        <v>192</v>
+        <v>176</v>
       </c>
     </row>
     <row r="15" spans="2:5">
       <c r="B15" s="4" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>213</v>
+        <v>197</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>214</v>
+        <v>198</v>
       </c>
       <c r="E15" s="27" t="s">
-        <v>192</v>
+        <v>176</v>
       </c>
     </row>
     <row r="16" spans="2:5">
       <c r="B16" s="4" t="s">
-        <v>215</v>
+        <v>199</v>
       </c>
       <c r="C16" s="27" t="s">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>217</v>
+        <v>201</v>
       </c>
       <c r="E16" s="27" t="s">
-        <v>192</v>
+        <v>176</v>
       </c>
     </row>
     <row r="17" spans="2:5">
       <c r="B17" s="4" t="s">
-        <v>218</v>
+        <v>202</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>219</v>
+        <v>203</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>220</v>
+        <v>204</v>
       </c>
       <c r="E17" s="27" t="s">
-        <v>192</v>
+        <v>176</v>
       </c>
     </row>
     <row r="18" spans="2:5">
       <c r="B18" s="4" t="s">
-        <v>221</v>
+        <v>205</v>
       </c>
       <c r="C18" s="27" t="s">
-        <v>222</v>
+        <v>206</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>223</v>
+        <v>207</v>
       </c>
       <c r="E18" s="27" t="s">
-        <v>192</v>
+        <v>176</v>
       </c>
     </row>
     <row r="19" spans="2:5">
       <c r="B19" s="4" t="s">
-        <v>224</v>
+        <v>208</v>
       </c>
       <c r="C19" s="27" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>226</v>
+        <v>210</v>
       </c>
       <c r="E19" s="27" t="s">
-        <v>192</v>
+        <v>176</v>
       </c>
     </row>
     <row r="20" spans="2:5">
       <c r="B20" s="4" t="s">
-        <v>227</v>
+        <v>211</v>
       </c>
       <c r="C20" s="27" t="s">
-        <v>228</v>
+        <v>212</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>229</v>
+        <v>213</v>
       </c>
       <c r="E20" s="27" t="s">
-        <v>192</v>
+        <v>176</v>
       </c>
     </row>
     <row r="21" spans="2:5">
       <c r="B21" s="4" t="s">
-        <v>230</v>
+        <v>214</v>
       </c>
       <c r="C21" s="27" t="s">
-        <v>231</v>
+        <v>215</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>232</v>
+        <v>216</v>
       </c>
       <c r="E21" s="27" t="s">
-        <v>192</v>
+        <v>176</v>
       </c>
     </row>
     <row r="22" spans="2:5">
       <c r="B22" s="4" t="s">
-        <v>233</v>
+        <v>217</v>
       </c>
       <c r="C22" s="27" t="s">
-        <v>234</v>
+        <v>218</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>235</v>
+        <v>219</v>
       </c>
       <c r="E22" s="27" t="s">
-        <v>192</v>
+        <v>176</v>
       </c>
     </row>
     <row r="23" spans="2:5">
       <c r="B23" s="4" t="s">
-        <v>236</v>
+        <v>220</v>
       </c>
       <c r="C23" s="27" t="s">
-        <v>237</v>
+        <v>221</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>238</v>
+        <v>222</v>
       </c>
       <c r="E23" s="27" t="s">
-        <v>192</v>
+        <v>176</v>
       </c>
     </row>
     <row r="24" spans="2:5">
       <c r="B24" s="4" t="s">
-        <v>239</v>
+        <v>223</v>
       </c>
       <c r="C24" s="27" t="s">
-        <v>240</v>
+        <v>224</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>241</v>
+        <v>225</v>
       </c>
       <c r="E24" s="27" t="s">
-        <v>192</v>
+        <v>176</v>
       </c>
     </row>
     <row r="26" spans="2:5">
       <c r="B26" s="3" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
@@ -10365,377 +10177,335 @@
     </row>
     <row r="27" spans="2:5">
       <c r="B27" s="10" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>243</v>
+        <v>227</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>244</v>
+        <v>228</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>204</v>
+        <v>188</v>
       </c>
     </row>
     <row r="28" spans="2:5">
       <c r="B28" s="4" t="s">
-        <v>245</v>
+        <v>229</v>
       </c>
       <c r="C28" s="28" t="s">
-        <v>246</v>
+        <v>230</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>247</v>
+        <v>231</v>
       </c>
       <c r="E28" s="28" t="s">
-        <v>194</v>
+        <v>178</v>
       </c>
     </row>
     <row r="29" spans="2:5">
       <c r="B29" s="4" t="s">
-        <v>248</v>
+        <v>232</v>
       </c>
       <c r="C29" s="28" t="s">
-        <v>249</v>
+        <v>233</v>
       </c>
       <c r="D29" s="11" t="s">
         <v>37</v>
       </c>
       <c r="E29" s="28" t="s">
-        <v>194</v>
+        <v>178</v>
       </c>
     </row>
     <row r="30" spans="2:5">
       <c r="B30" s="4" t="s">
-        <v>250</v>
+        <v>234</v>
       </c>
       <c r="C30" s="28" t="s">
-        <v>251</v>
+        <v>235</v>
       </c>
       <c r="D30" s="11" t="s">
         <v>43</v>
       </c>
       <c r="E30" s="28" t="s">
-        <v>194</v>
+        <v>178</v>
       </c>
     </row>
     <row r="31" spans="2:5">
       <c r="B31" s="4" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="C31" s="28" t="s">
-        <v>252</v>
+        <v>236</v>
       </c>
       <c r="D31" s="11" t="s">
         <v>31</v>
       </c>
       <c r="E31" s="28" t="s">
-        <v>194</v>
+        <v>178</v>
       </c>
     </row>
     <row r="32" spans="2:5">
       <c r="B32" s="4" t="s">
-        <v>253</v>
+        <v>237</v>
       </c>
       <c r="C32" s="28" t="s">
-        <v>254</v>
+        <v>238</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>255</v>
+        <v>239</v>
       </c>
       <c r="E32" s="28" t="s">
-        <v>194</v>
+        <v>178</v>
       </c>
     </row>
     <row r="33" spans="2:5">
       <c r="B33" s="4" t="s">
-        <v>256</v>
+        <v>240</v>
       </c>
       <c r="C33" s="28" t="s">
-        <v>257</v>
+        <v>241</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>258</v>
+        <v>242</v>
       </c>
       <c r="E33" s="28" t="s">
-        <v>194</v>
+        <v>178</v>
       </c>
     </row>
     <row r="34" spans="2:5">
       <c r="B34" s="4" t="s">
-        <v>259</v>
+        <v>243</v>
       </c>
       <c r="C34" s="28" t="s">
-        <v>260</v>
+        <v>244</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>261</v>
+        <v>245</v>
       </c>
       <c r="E34" s="28" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="35" spans="2:5">
-      <c r="B35" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="C35" s="28" t="s">
-        <v>263</v>
-      </c>
-      <c r="D35" s="11" t="s">
-        <v>264</v>
-      </c>
-      <c r="E35" s="28" t="s">
-        <v>194</v>
-      </c>
+        <v>178</v>
+      </c>
+    </row>
+    <row r="36" spans="2:5">
+      <c r="B36" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="C36" s="3"/>
+      <c r="D36" s="3"/>
+      <c r="E36" s="3"/>
     </row>
     <row r="37" spans="2:5">
-      <c r="B37" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="C37" s="3"/>
-      <c r="D37" s="3"/>
-      <c r="E37" s="3"/>
-    </row>
-    <row r="38" spans="2:5">
-      <c r="B38" s="10" t="s">
-        <v>266</v>
-      </c>
-      <c r="C38" s="10" t="s">
-        <v>267</v>
-      </c>
-      <c r="D38" s="10" t="s">
-        <v>268</v>
-      </c>
-      <c r="E38" s="10" t="s">
-        <v>204</v>
+      <c r="B37" s="10" t="s">
+        <v>247</v>
+      </c>
+      <c r="C37" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="D37" s="10" t="s">
+        <v>249</v>
+      </c>
+      <c r="E37" s="10" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="38" spans="2:5" ht="35" customHeight="1">
+      <c r="B38" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="C38" s="29" t="s">
+        <v>251</v>
+      </c>
+      <c r="D38" s="11" t="s">
+        <v>252</v>
+      </c>
+      <c r="E38" s="29" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="39" spans="2:5" ht="35" customHeight="1">
       <c r="B39" s="4" t="s">
-        <v>269</v>
+        <v>253</v>
       </c>
       <c r="C39" s="29" t="s">
-        <v>270</v>
+        <v>254</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>271</v>
+        <v>255</v>
       </c>
       <c r="E39" s="29" t="s">
-        <v>196</v>
+        <v>180</v>
       </c>
     </row>
     <row r="40" spans="2:5" ht="35" customHeight="1">
       <c r="B40" s="4" t="s">
-        <v>272</v>
+        <v>256</v>
       </c>
       <c r="C40" s="29" t="s">
-        <v>273</v>
+        <v>257</v>
       </c>
       <c r="D40" s="11" t="s">
-        <v>274</v>
+        <v>258</v>
       </c>
       <c r="E40" s="29" t="s">
-        <v>196</v>
+        <v>180</v>
       </c>
     </row>
     <row r="41" spans="2:5" ht="35" customHeight="1">
       <c r="B41" s="4" t="s">
-        <v>275</v>
+        <v>259</v>
       </c>
       <c r="C41" s="29" t="s">
-        <v>276</v>
+        <v>260</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>277</v>
+        <v>261</v>
       </c>
       <c r="E41" s="29" t="s">
-        <v>196</v>
+        <v>180</v>
       </c>
     </row>
     <row r="42" spans="2:5" ht="35" customHeight="1">
       <c r="B42" s="4" t="s">
-        <v>278</v>
+        <v>262</v>
       </c>
       <c r="C42" s="29" t="s">
-        <v>279</v>
+        <v>263</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>280</v>
+        <v>264</v>
       </c>
       <c r="E42" s="29" t="s">
-        <v>196</v>
+        <v>180</v>
       </c>
     </row>
     <row r="43" spans="2:5" ht="35" customHeight="1">
       <c r="B43" s="4" t="s">
-        <v>281</v>
+        <v>265</v>
       </c>
       <c r="C43" s="29" t="s">
-        <v>282</v>
+        <v>266</v>
       </c>
       <c r="D43" s="11" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="E43" s="29" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="44" spans="2:5" ht="35" customHeight="1">
-      <c r="B44" s="4" t="s">
-        <v>284</v>
-      </c>
-      <c r="C44" s="29" t="s">
-        <v>285</v>
-      </c>
-      <c r="D44" s="11" t="s">
-        <v>286</v>
-      </c>
-      <c r="E44" s="29" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="45" spans="2:5" ht="35" customHeight="1">
-      <c r="B45" s="4" t="s">
-        <v>287</v>
-      </c>
-      <c r="C45" s="29" t="s">
-        <v>288</v>
-      </c>
-      <c r="D45" s="11" t="s">
-        <v>289</v>
-      </c>
-      <c r="E45" s="29" t="s">
-        <v>196</v>
+        <v>180</v>
+      </c>
+    </row>
+    <row r="45" spans="2:5">
+      <c r="B45" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="C45" s="3"/>
+      <c r="D45" s="3"/>
+      <c r="E45" s="3"/>
+    </row>
+    <row r="46" spans="2:5">
+      <c r="B46" s="10" t="s">
+        <v>269</v>
+      </c>
+      <c r="C46" s="10" t="s">
+        <v>270</v>
+      </c>
+      <c r="D46" s="10" t="s">
+        <v>271</v>
+      </c>
+      <c r="E46" s="10" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="47" spans="2:5">
-      <c r="B47" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="C47" s="3"/>
-      <c r="D47" s="3"/>
-      <c r="E47" s="3"/>
+      <c r="B47" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="C47" s="30" t="s">
+        <v>273</v>
+      </c>
+      <c r="D47" s="11" t="s">
+        <v>274</v>
+      </c>
+      <c r="E47" s="30" t="s">
+        <v>182</v>
+      </c>
     </row>
     <row r="48" spans="2:5">
-      <c r="B48" s="10" t="s">
-        <v>291</v>
-      </c>
-      <c r="C48" s="10" t="s">
-        <v>292</v>
-      </c>
-      <c r="D48" s="10" t="s">
-        <v>293</v>
-      </c>
-      <c r="E48" s="10" t="s">
-        <v>204</v>
+      <c r="B48" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="C48" s="30" t="s">
+        <v>276</v>
+      </c>
+      <c r="D48" s="11" t="s">
+        <v>277</v>
+      </c>
+      <c r="E48" s="30" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="49" spans="2:5">
       <c r="B49" s="4" t="s">
-        <v>294</v>
+        <v>278</v>
       </c>
       <c r="C49" s="30" t="s">
-        <v>295</v>
+        <v>279</v>
       </c>
       <c r="D49" s="11" t="s">
-        <v>296</v>
+        <v>280</v>
       </c>
       <c r="E49" s="30" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="50" spans="2:5">
       <c r="B50" s="4" t="s">
-        <v>297</v>
+        <v>281</v>
       </c>
       <c r="C50" s="30" t="s">
-        <v>298</v>
+        <v>282</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>299</v>
+        <v>283</v>
       </c>
       <c r="E50" s="30" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="51" spans="2:5">
       <c r="B51" s="4" t="s">
-        <v>300</v>
+        <v>284</v>
       </c>
       <c r="C51" s="30" t="s">
-        <v>301</v>
+        <v>285</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>302</v>
+        <v>286</v>
       </c>
       <c r="E51" s="30" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="52" spans="2:5">
       <c r="B52" s="4" t="s">
-        <v>303</v>
+        <v>287</v>
       </c>
       <c r="C52" s="30" t="s">
-        <v>304</v>
+        <v>288</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>305</v>
+        <v>289</v>
       </c>
       <c r="E52" s="30" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="53" spans="2:5">
-      <c r="B53" s="4" t="s">
-        <v>306</v>
-      </c>
-      <c r="C53" s="30" t="s">
-        <v>307</v>
-      </c>
-      <c r="D53" s="11" t="s">
-        <v>308</v>
-      </c>
-      <c r="E53" s="30" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="54" spans="2:5">
-      <c r="B54" s="4" t="s">
-        <v>309</v>
-      </c>
-      <c r="C54" s="30" t="s">
-        <v>310</v>
-      </c>
-      <c r="D54" s="11" t="s">
-        <v>311</v>
-      </c>
-      <c r="E54" s="30" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="55" spans="2:5">
-      <c r="B55" s="4" t="s">
-        <v>312</v>
-      </c>
-      <c r="C55" s="30" t="s">
-        <v>313</v>
-      </c>
-      <c r="D55" s="11" t="s">
-        <v>314</v>
-      </c>
-      <c r="E55" s="30" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="58" spans="2:5">
-      <c r="B58" s="6" t="s">
-        <v>315</v>
-      </c>
-      <c r="C58" s="6"/>
-      <c r="D58" s="6"/>
-      <c r="E58" s="6"/>
+      <c r="B55" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="C55" s="6"/>
+      <c r="D55" s="6"/>
+      <c r="E55" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -10743,9 +10513,9 @@
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="B10:E10"/>
     <mergeCell ref="B26:E26"/>
-    <mergeCell ref="B37:E37"/>
-    <mergeCell ref="B47:E47"/>
-    <mergeCell ref="B58:E58"/>
+    <mergeCell ref="B36:E36"/>
+    <mergeCell ref="B45:E45"/>
+    <mergeCell ref="B55:E55"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
